--- a/data/bars.xlsx
+++ b/data/bars.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Natha\projects_and_clubs\Queen-s-Engineering-Jacket-GPA-Planner\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4206DB98-3746-4A94-9ED8-875EECDE57E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A87C7A-EBE2-4345-8988-81931EDEB8C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1C6F1F17-E6F1-46B7-9E88-A2681932F042}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7639" uniqueCount="1655">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7749" uniqueCount="1655">
   <si>
     <t>include</t>
   </si>
@@ -8955,7 +8955,7 @@
         <v>230</v>
       </c>
       <c r="C100" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D100" t="s">
         <v>13</v>
@@ -9060,7 +9060,7 @@
         <v>236</v>
       </c>
       <c r="C103" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D103" t="s">
         <v>13</v>
@@ -9130,7 +9130,7 @@
         <v>240</v>
       </c>
       <c r="C105" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D105" t="s">
         <v>13</v>
@@ -9165,7 +9165,7 @@
         <v>242</v>
       </c>
       <c r="C106" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D106" t="s">
         <v>13</v>
@@ -9514,9 +9514,6 @@
       <c r="B116" t="s">
         <v>265</v>
       </c>
-      <c r="C116" t="s">
-        <v>13</v>
-      </c>
       <c r="D116" t="s">
         <v>13</v>
       </c>
@@ -9725,7 +9722,7 @@
         <v>277</v>
       </c>
       <c r="C122" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D122" t="s">
         <v>13</v>
@@ -10110,7 +10107,7 @@
         <v>301</v>
       </c>
       <c r="C133" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D133" t="s">
         <v>13</v>
@@ -10145,7 +10142,7 @@
         <v>303</v>
       </c>
       <c r="C134" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D134" t="s">
         <v>13</v>
@@ -10180,7 +10177,7 @@
         <v>305</v>
       </c>
       <c r="C135" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D135" t="s">
         <v>13</v>
@@ -10215,7 +10212,7 @@
         <v>307</v>
       </c>
       <c r="C136" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D136" t="s">
         <v>13</v>
@@ -10250,7 +10247,7 @@
         <v>309</v>
       </c>
       <c r="C137" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D137" t="s">
         <v>13</v>
@@ -10320,7 +10317,7 @@
         <v>313</v>
       </c>
       <c r="C139" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D139" t="s">
         <v>13</v>
@@ -10355,7 +10352,7 @@
         <v>315</v>
       </c>
       <c r="C140" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D140" t="s">
         <v>13</v>
@@ -10530,7 +10527,7 @@
         <v>325</v>
       </c>
       <c r="C145" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D145" t="s">
         <v>13</v>
@@ -10635,7 +10632,7 @@
         <v>331</v>
       </c>
       <c r="C148" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D148" t="s">
         <v>13</v>
@@ -10705,7 +10702,7 @@
         <v>335</v>
       </c>
       <c r="C150" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D150" t="s">
         <v>13</v>
@@ -10810,7 +10807,7 @@
         <v>341</v>
       </c>
       <c r="C153" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D153" t="s">
         <v>13</v>
@@ -10880,7 +10877,7 @@
         <v>345</v>
       </c>
       <c r="C155" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D155" t="s">
         <v>13</v>
@@ -10950,7 +10947,7 @@
         <v>349</v>
       </c>
       <c r="C157" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D157" t="s">
         <v>13</v>
@@ -11084,13 +11081,13 @@
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="B161" t="s">
         <v>357</v>
       </c>
       <c r="C161" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="D161" t="s">
         <v>13</v>
@@ -11125,7 +11122,7 @@
         <v>359</v>
       </c>
       <c r="C162" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D162" t="s">
         <v>13</v>
@@ -11195,7 +11192,7 @@
         <v>363</v>
       </c>
       <c r="C164" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D164" t="s">
         <v>13</v>
@@ -11265,7 +11262,7 @@
         <v>367</v>
       </c>
       <c r="C166" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D166" t="s">
         <v>13</v>
@@ -11300,7 +11297,7 @@
         <v>369</v>
       </c>
       <c r="C167" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D167" t="s">
         <v>13</v>
@@ -11335,7 +11332,7 @@
         <v>371</v>
       </c>
       <c r="C168" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D168" t="s">
         <v>13</v>
@@ -11370,7 +11367,7 @@
         <v>373</v>
       </c>
       <c r="C169" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D169" t="s">
         <v>13</v>
@@ -11440,7 +11437,7 @@
         <v>377</v>
       </c>
       <c r="C171" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D171" t="s">
         <v>13</v>
@@ -11510,7 +11507,7 @@
         <v>382</v>
       </c>
       <c r="C173" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D173" t="s">
         <v>13</v>
@@ -11545,7 +11542,7 @@
         <v>384</v>
       </c>
       <c r="C174" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D174" t="s">
         <v>13</v>
@@ -11580,7 +11577,7 @@
         <v>386</v>
       </c>
       <c r="C175" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D175" t="s">
         <v>13</v>
@@ -11615,7 +11612,7 @@
         <v>388</v>
       </c>
       <c r="C176" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D176" t="s">
         <v>13</v>
@@ -11650,7 +11647,7 @@
         <v>390</v>
       </c>
       <c r="C177" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D177" t="s">
         <v>13</v>
@@ -11685,7 +11682,7 @@
         <v>392</v>
       </c>
       <c r="C178" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D178" t="s">
         <v>13</v>
@@ -11720,7 +11717,7 @@
         <v>394</v>
       </c>
       <c r="C179" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D179" t="s">
         <v>13</v>
@@ -11784,13 +11781,13 @@
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="B181" t="s">
         <v>398</v>
       </c>
       <c r="C181" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="D181" t="s">
         <v>13</v>
@@ -11825,7 +11822,7 @@
         <v>400</v>
       </c>
       <c r="C182" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D182" t="s">
         <v>13</v>
@@ -11860,7 +11857,7 @@
         <v>402</v>
       </c>
       <c r="C183" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D183" t="s">
         <v>13</v>
@@ -11895,7 +11892,7 @@
         <v>404</v>
       </c>
       <c r="C184" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D184" t="s">
         <v>13</v>
@@ -11965,7 +11962,7 @@
         <v>409</v>
       </c>
       <c r="C186" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D186" t="s">
         <v>13</v>
@@ -12035,7 +12032,7 @@
         <v>414</v>
       </c>
       <c r="C188" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D188" t="s">
         <v>13</v>
@@ -12140,7 +12137,7 @@
         <v>421</v>
       </c>
       <c r="C191" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D191" t="s">
         <v>13</v>
@@ -12175,7 +12172,7 @@
         <v>423</v>
       </c>
       <c r="C192" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D192" t="s">
         <v>13</v>
@@ -12245,7 +12242,7 @@
         <v>428</v>
       </c>
       <c r="C194" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D194" t="s">
         <v>13</v>
@@ -12315,7 +12312,7 @@
         <v>432</v>
       </c>
       <c r="C196" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D196" t="s">
         <v>13</v>
@@ -12350,7 +12347,7 @@
         <v>434</v>
       </c>
       <c r="C197" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D197" t="s">
         <v>13</v>
@@ -12385,7 +12382,7 @@
         <v>436</v>
       </c>
       <c r="C198" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D198" t="s">
         <v>13</v>
@@ -12420,7 +12417,7 @@
         <v>438</v>
       </c>
       <c r="C199" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D199" t="s">
         <v>13</v>
@@ -12490,7 +12487,7 @@
         <v>442</v>
       </c>
       <c r="C201" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D201" t="s">
         <v>13</v>
@@ -12525,7 +12522,7 @@
         <v>444</v>
       </c>
       <c r="C202" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D202" t="s">
         <v>13</v>
@@ -12560,7 +12557,7 @@
         <v>446</v>
       </c>
       <c r="C203" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D203" t="s">
         <v>13</v>
@@ -12595,7 +12592,7 @@
         <v>448</v>
       </c>
       <c r="C204" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D204" t="s">
         <v>13</v>
@@ -12630,7 +12627,7 @@
         <v>450</v>
       </c>
       <c r="C205" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D205" t="s">
         <v>13</v>
@@ -12665,7 +12662,7 @@
         <v>452</v>
       </c>
       <c r="C206" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D206" t="s">
         <v>13</v>
@@ -12700,7 +12697,7 @@
         <v>454</v>
       </c>
       <c r="C207" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D207" t="s">
         <v>13</v>
@@ -12805,7 +12802,7 @@
         <v>460</v>
       </c>
       <c r="C210" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D210" t="s">
         <v>13</v>
@@ -12910,7 +12907,7 @@
         <v>466</v>
       </c>
       <c r="C213" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D213" t="s">
         <v>13</v>
@@ -12945,7 +12942,7 @@
         <v>468</v>
       </c>
       <c r="C214" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D214" t="s">
         <v>13</v>
@@ -12974,13 +12971,13 @@
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="B215" t="s">
         <v>470</v>
       </c>
       <c r="C215" t="s">
-        <v>13</v>
+        <v>100</v>
       </c>
       <c r="D215" t="s">
         <v>13</v>
@@ -13015,7 +13012,7 @@
         <v>472</v>
       </c>
       <c r="C216" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D216" t="s">
         <v>13</v>
@@ -13050,7 +13047,7 @@
         <v>474</v>
       </c>
       <c r="C217" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D217" t="s">
         <v>13</v>
@@ -13120,7 +13117,7 @@
         <v>478</v>
       </c>
       <c r="C219" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D219" t="s">
         <v>13</v>
@@ -13155,7 +13152,7 @@
         <v>480</v>
       </c>
       <c r="C220" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D220" t="s">
         <v>13</v>
@@ -13190,7 +13187,7 @@
         <v>482</v>
       </c>
       <c r="C221" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D221" t="s">
         <v>13</v>
@@ -13225,7 +13222,7 @@
         <v>484</v>
       </c>
       <c r="C222" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D222" t="s">
         <v>13</v>
@@ -13400,7 +13397,7 @@
         <v>495</v>
       </c>
       <c r="C227" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D227" t="s">
         <v>13</v>
@@ -13435,7 +13432,7 @@
         <v>497</v>
       </c>
       <c r="C228" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D228" t="s">
         <v>13</v>
@@ -13540,7 +13537,7 @@
         <v>503</v>
       </c>
       <c r="C231" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D231" t="s">
         <v>13</v>
@@ -13575,7 +13572,7 @@
         <v>505</v>
       </c>
       <c r="C232" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D232" t="s">
         <v>13</v>
@@ -13645,7 +13642,7 @@
         <v>508</v>
       </c>
       <c r="C234" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D234" t="s">
         <v>13</v>
@@ -13785,7 +13782,7 @@
         <v>516</v>
       </c>
       <c r="C238" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D238" t="s">
         <v>13</v>
@@ -13820,7 +13817,7 @@
         <v>518</v>
       </c>
       <c r="C239" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D239" t="s">
         <v>13</v>
@@ -13890,7 +13887,7 @@
         <v>522</v>
       </c>
       <c r="C241" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D241" t="s">
         <v>13</v>
@@ -14030,7 +14027,7 @@
         <v>530</v>
       </c>
       <c r="C245" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D245" t="s">
         <v>13</v>
@@ -14065,7 +14062,7 @@
         <v>532</v>
       </c>
       <c r="C246" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D246" t="s">
         <v>13</v>
@@ -14100,7 +14097,7 @@
         <v>534</v>
       </c>
       <c r="C247" t="s">
-        <v>13</v>
+        <v>65</v>
       </c>
       <c r="D247" t="s">
         <v>13</v>
@@ -14135,7 +14132,7 @@
         <v>536</v>
       </c>
       <c r="C248" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D248" t="s">
         <v>13</v>
@@ -14520,7 +14517,7 @@
         <v>559</v>
       </c>
       <c r="C259" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D259" t="s">
         <v>13</v>

--- a/data/bars.xlsx
+++ b/data/bars.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Natha\projects_and_clubs\Queen-s-Engineering-Jacket-GPA-Planner\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF978DE5-34D5-4400-84F1-9807FD468F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CBF795-1508-4D57-92DE-CB30F721F433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1C6F1F17-E6F1-46B7-9E88-A2681932F042}"/>
   </bookViews>
@@ -6886,13 +6886,13 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>11</v>
       </c>
       <c r="B38" t="s">
         <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="D38" t="s">
         <v>13</v>

--- a/data/bars.xlsx
+++ b/data/bars.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Natha\projects_and_clubs\Queen-s-Engineering-Jacket-GPA-Planner\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CBF795-1508-4D57-92DE-CB30F721F433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944C26D7-01CC-4964-8B38-4411D6FF6379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1C6F1F17-E6F1-46B7-9E88-A2681932F042}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">bars!$A$1:$K$796</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">bars!$A$1:$K$797</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7174" uniqueCount="1668">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7177" uniqueCount="1669">
   <si>
     <t>include</t>
   </si>
@@ -5055,6 +5055,9 @@
   </si>
   <si>
     <t>oxidizing / biohazard</t>
+  </si>
+  <si>
+    <t>100 mile rocky road</t>
   </si>
 </sst>
 </file>
@@ -5186,8 +5189,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61F6FD9B-E393-44E1-A28B-1A58FAFCE26B}" name="bars" displayName="bars" ref="A1:O796" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:O796" xr:uid="{61F6FD9B-E393-44E1-A28B-1A58FAFCE26B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61F6FD9B-E393-44E1-A28B-1A58FAFCE26B}" name="bars" displayName="bars" ref="A1:O797" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:O797" xr:uid="{61F6FD9B-E393-44E1-A28B-1A58FAFCE26B}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{54CFF86C-F58D-4990-9537-B4399AF90F41}" uniqueName="1" name="include" queryTableFieldId="1" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{3F04A84D-B75B-4711-88E7-E74320EFE40C}" uniqueName="2" name="name" queryTableFieldId="2" dataDxfId="11"/>
@@ -5526,7 +5529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30AEC9F1-41AD-43D9-B162-BDFD4A7D5019}">
-  <dimension ref="A1:O796"/>
+  <dimension ref="A1:O797"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
@@ -5622,7 +5625,6 @@
       <c r="K2" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="2"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
@@ -5658,7 +5660,6 @@
       <c r="K3" t="s">
         <v>13</v>
       </c>
-      <c r="O3" s="2"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -5694,7 +5695,6 @@
       <c r="K4" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="2"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
@@ -5730,7 +5730,6 @@
       <c r="K5" t="s">
         <v>13</v>
       </c>
-      <c r="O5" s="2"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
@@ -5766,7 +5765,6 @@
       <c r="K6" t="s">
         <v>13</v>
       </c>
-      <c r="O6" s="2"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
@@ -5802,7 +5800,6 @@
       <c r="K7" t="s">
         <v>13</v>
       </c>
-      <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
@@ -5838,7 +5835,6 @@
       <c r="K8" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="2"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -5874,7 +5870,6 @@
       <c r="K9" t="s">
         <v>13</v>
       </c>
-      <c r="O9" s="2"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
@@ -5910,7 +5905,6 @@
       <c r="K10" t="s">
         <v>13</v>
       </c>
-      <c r="O10" s="2"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -5946,7 +5940,6 @@
       <c r="K11" t="s">
         <v>13</v>
       </c>
-      <c r="O11" s="2"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -5982,7 +5975,6 @@
       <c r="K12" t="s">
         <v>13</v>
       </c>
-      <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -6018,7 +6010,6 @@
       <c r="K13" t="s">
         <v>13</v>
       </c>
-      <c r="O13" s="2"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
@@ -6054,7 +6045,6 @@
       <c r="K14" t="s">
         <v>13</v>
       </c>
-      <c r="O14" s="2"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -6090,7 +6080,6 @@
       <c r="K15" t="s">
         <v>13</v>
       </c>
-      <c r="O15" s="2"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -6126,9 +6115,8 @@
       <c r="K16" t="s">
         <v>44</v>
       </c>
-      <c r="O16" s="2"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -6162,9 +6150,8 @@
       <c r="K17" t="s">
         <v>13</v>
       </c>
-      <c r="O17" s="2"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>98</v>
       </c>
@@ -6198,9 +6185,8 @@
       <c r="K18" t="s">
         <v>13</v>
       </c>
-      <c r="O18" s="2"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -6234,9 +6220,8 @@
       <c r="K19" t="s">
         <v>13</v>
       </c>
-      <c r="O19" s="2"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -6270,9 +6255,8 @@
       <c r="K20" t="s">
         <v>13</v>
       </c>
-      <c r="O20" s="2"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -6306,9 +6290,8 @@
       <c r="K21" t="s">
         <v>13</v>
       </c>
-      <c r="O21" s="2"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -6342,9 +6325,8 @@
       <c r="K22" t="s">
         <v>13</v>
       </c>
-      <c r="O22" s="2"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -6378,9 +6360,8 @@
       <c r="K23" t="s">
         <v>13</v>
       </c>
-      <c r="O23" s="2"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -6414,9 +6395,8 @@
       <c r="K24" t="s">
         <v>13</v>
       </c>
-      <c r="O24" s="2"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -6450,9 +6430,8 @@
       <c r="K25" t="s">
         <v>13</v>
       </c>
-      <c r="O25" s="2"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -6486,9 +6465,8 @@
       <c r="K26" t="s">
         <v>13</v>
       </c>
-      <c r="O26" s="2"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>98</v>
       </c>
@@ -6522,9 +6500,8 @@
       <c r="K27" t="s">
         <v>13</v>
       </c>
-      <c r="O27" s="2"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -6558,9 +6535,8 @@
       <c r="K28" t="s">
         <v>13</v>
       </c>
-      <c r="O28" s="2"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -6594,9 +6570,8 @@
       <c r="K29" t="s">
         <v>13</v>
       </c>
-      <c r="O29" s="2"/>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -6630,9 +6605,8 @@
       <c r="K30" t="s">
         <v>13</v>
       </c>
-      <c r="O30" s="2"/>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -6666,9 +6640,8 @@
       <c r="K31" t="s">
         <v>13</v>
       </c>
-      <c r="O31" s="2"/>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -6702,9 +6675,8 @@
       <c r="K32" t="s">
         <v>13</v>
       </c>
-      <c r="O32" s="2"/>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -6738,9 +6710,8 @@
       <c r="K33" t="s">
         <v>13</v>
       </c>
-      <c r="O33" s="2"/>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -6774,9 +6745,8 @@
       <c r="K34" t="s">
         <v>13</v>
       </c>
-      <c r="O34" s="2"/>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>11</v>
       </c>
@@ -6810,9 +6780,8 @@
       <c r="K35" t="s">
         <v>13</v>
       </c>
-      <c r="O35" s="2"/>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>11</v>
       </c>
@@ -6846,9 +6815,8 @@
       <c r="K36" t="s">
         <v>13</v>
       </c>
-      <c r="O36" s="2"/>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -6882,9 +6850,8 @@
       <c r="K37" t="s">
         <v>13</v>
       </c>
-      <c r="O37" s="2"/>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -6918,9 +6885,8 @@
       <c r="K38" t="s">
         <v>13</v>
       </c>
-      <c r="O38" s="2"/>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>11</v>
       </c>
@@ -6954,9 +6920,8 @@
       <c r="K39" t="s">
         <v>13</v>
       </c>
-      <c r="O39" s="2"/>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>11</v>
       </c>
@@ -6990,9 +6955,8 @@
       <c r="K40" t="s">
         <v>13</v>
       </c>
-      <c r="O40" s="2"/>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>11</v>
       </c>
@@ -7026,9 +6990,8 @@
       <c r="K41" t="s">
         <v>13</v>
       </c>
-      <c r="O41" s="2"/>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>11</v>
       </c>
@@ -7062,9 +7025,8 @@
       <c r="K42" t="s">
         <v>13</v>
       </c>
-      <c r="O42" s="2"/>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>11</v>
       </c>
@@ -7098,9 +7060,8 @@
       <c r="K43" t="s">
         <v>13</v>
       </c>
-      <c r="O43" s="2"/>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -7134,9 +7095,8 @@
       <c r="K44" t="s">
         <v>13</v>
       </c>
-      <c r="O44" s="2"/>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>11</v>
       </c>
@@ -7170,9 +7130,8 @@
       <c r="K45" t="s">
         <v>13</v>
       </c>
-      <c r="O45" s="2"/>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -7206,9 +7165,8 @@
       <c r="K46" t="s">
         <v>13</v>
       </c>
-      <c r="O46" s="2"/>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -7242,9 +7200,8 @@
       <c r="K47" t="s">
         <v>13</v>
       </c>
-      <c r="O47" s="2"/>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>11</v>
       </c>
@@ -7278,9 +7235,8 @@
       <c r="K48" t="s">
         <v>13</v>
       </c>
-      <c r="O48" s="2"/>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>11</v>
       </c>
@@ -7314,9 +7270,8 @@
       <c r="K49" t="s">
         <v>13</v>
       </c>
-      <c r="O49" s="2"/>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>98</v>
       </c>
@@ -7350,9 +7305,8 @@
       <c r="K50" t="s">
         <v>13</v>
       </c>
-      <c r="O50" s="2"/>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>11</v>
       </c>
@@ -7386,9 +7340,8 @@
       <c r="K51" t="s">
         <v>13</v>
       </c>
-      <c r="O51" s="2"/>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>11</v>
       </c>
@@ -7422,9 +7375,8 @@
       <c r="K52" t="s">
         <v>13</v>
       </c>
-      <c r="O52" s="2"/>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>11</v>
       </c>
@@ -7458,9 +7410,8 @@
       <c r="K53" t="s">
         <v>13</v>
       </c>
-      <c r="O53" s="2"/>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>98</v>
       </c>
@@ -7494,9 +7445,8 @@
       <c r="K54" t="s">
         <v>13</v>
       </c>
-      <c r="O54" s="2"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>98</v>
       </c>
@@ -7530,9 +7480,8 @@
       <c r="K55" t="s">
         <v>13</v>
       </c>
-      <c r="O55" s="2"/>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -7566,9 +7515,8 @@
       <c r="K56" t="s">
         <v>13</v>
       </c>
-      <c r="O56" s="2"/>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>11</v>
       </c>
@@ -7602,9 +7550,8 @@
       <c r="K57" t="s">
         <v>13</v>
       </c>
-      <c r="O57" s="2"/>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>11</v>
       </c>
@@ -7638,9 +7585,8 @@
       <c r="K58" t="s">
         <v>13</v>
       </c>
-      <c r="O58" s="2"/>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>11</v>
       </c>
@@ -7674,9 +7620,8 @@
       <c r="K59" t="s">
         <v>13</v>
       </c>
-      <c r="O59" s="2"/>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>11</v>
       </c>
@@ -7710,9 +7655,8 @@
       <c r="K60" t="s">
         <v>13</v>
       </c>
-      <c r="O60" s="2"/>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>11</v>
       </c>
@@ -7746,9 +7690,8 @@
       <c r="K61" t="s">
         <v>13</v>
       </c>
-      <c r="O61" s="2"/>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>11</v>
       </c>
@@ -7782,9 +7725,8 @@
       <c r="K62" t="s">
         <v>13</v>
       </c>
-      <c r="O62" s="2"/>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>11</v>
       </c>
@@ -7818,9 +7760,8 @@
       <c r="K63" t="s">
         <v>13</v>
       </c>
-      <c r="O63" s="2"/>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>98</v>
       </c>
@@ -7854,9 +7795,8 @@
       <c r="K64" t="s">
         <v>13</v>
       </c>
-      <c r="O64" s="2"/>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>11</v>
       </c>
@@ -7890,9 +7830,8 @@
       <c r="K65" t="s">
         <v>13</v>
       </c>
-      <c r="O65" s="2"/>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>11</v>
       </c>
@@ -7926,9 +7865,8 @@
       <c r="K66" t="s">
         <v>13</v>
       </c>
-      <c r="O66" s="2"/>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>11</v>
       </c>
@@ -7962,9 +7900,8 @@
       <c r="K67" t="s">
         <v>13</v>
       </c>
-      <c r="O67" s="2"/>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>11</v>
       </c>
@@ -7998,9 +7935,8 @@
       <c r="K68" t="s">
         <v>13</v>
       </c>
-      <c r="O68" s="2"/>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>11</v>
       </c>
@@ -8034,9 +7970,8 @@
       <c r="K69" t="s">
         <v>13</v>
       </c>
-      <c r="O69" s="2"/>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>11</v>
       </c>
@@ -8070,9 +8005,8 @@
       <c r="K70" t="s">
         <v>13</v>
       </c>
-      <c r="O70" s="2"/>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -8106,9 +8040,8 @@
       <c r="K71" t="s">
         <v>13</v>
       </c>
-      <c r="O71" s="2"/>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>11</v>
       </c>
@@ -8142,9 +8075,8 @@
       <c r="K72" t="s">
         <v>13</v>
       </c>
-      <c r="O72" s="2"/>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>11</v>
       </c>
@@ -8178,9 +8110,8 @@
       <c r="K73" t="s">
         <v>13</v>
       </c>
-      <c r="O73" s="2"/>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>11</v>
       </c>
@@ -8214,9 +8145,8 @@
       <c r="K74" t="s">
         <v>13</v>
       </c>
-      <c r="O74" s="2"/>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>11</v>
       </c>
@@ -8250,9 +8180,8 @@
       <c r="K75" t="s">
         <v>13</v>
       </c>
-      <c r="O75" s="2"/>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>11</v>
       </c>
@@ -8286,9 +8215,8 @@
       <c r="K76" t="s">
         <v>13</v>
       </c>
-      <c r="O76" s="2"/>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>11</v>
       </c>
@@ -8322,9 +8250,8 @@
       <c r="K77" t="s">
         <v>13</v>
       </c>
-      <c r="O77" s="2"/>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>11</v>
       </c>
@@ -8358,9 +8285,8 @@
       <c r="K78" t="s">
         <v>13</v>
       </c>
-      <c r="O78" s="2"/>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>98</v>
       </c>
@@ -8394,9 +8320,8 @@
       <c r="K79" t="s">
         <v>13</v>
       </c>
-      <c r="O79" s="2"/>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>11</v>
       </c>
@@ -8430,9 +8355,8 @@
       <c r="K80" t="s">
         <v>13</v>
       </c>
-      <c r="O80" s="2"/>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>11</v>
       </c>
@@ -8466,9 +8390,8 @@
       <c r="K81" t="s">
         <v>13</v>
       </c>
-      <c r="O81" s="2"/>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>11</v>
       </c>
@@ -8502,9 +8425,8 @@
       <c r="K82" t="s">
         <v>13</v>
       </c>
-      <c r="O82" s="2"/>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>11</v>
       </c>
@@ -8538,9 +8460,8 @@
       <c r="K83" t="s">
         <v>13</v>
       </c>
-      <c r="O83" s="2"/>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>11</v>
       </c>
@@ -8574,9 +8495,8 @@
       <c r="K84" t="s">
         <v>13</v>
       </c>
-      <c r="O84" s="2"/>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>11</v>
       </c>
@@ -8610,9 +8530,8 @@
       <c r="K85" t="s">
         <v>13</v>
       </c>
-      <c r="O85" s="2"/>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>11</v>
       </c>
@@ -8646,9 +8565,8 @@
       <c r="K86" t="s">
         <v>13</v>
       </c>
-      <c r="O86" s="2"/>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>11</v>
       </c>
@@ -8682,9 +8600,8 @@
       <c r="K87" t="s">
         <v>13</v>
       </c>
-      <c r="O87" s="2"/>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>11</v>
       </c>
@@ -8718,9 +8635,8 @@
       <c r="K88" t="s">
         <v>13</v>
       </c>
-      <c r="O88" s="2"/>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>11</v>
       </c>
@@ -8754,9 +8670,8 @@
       <c r="K89" t="s">
         <v>13</v>
       </c>
-      <c r="O89" s="2"/>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>11</v>
       </c>
@@ -8790,9 +8705,8 @@
       <c r="K90" t="s">
         <v>13</v>
       </c>
-      <c r="O90" s="2"/>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>11</v>
       </c>
@@ -8826,9 +8740,8 @@
       <c r="K91" t="s">
         <v>13</v>
       </c>
-      <c r="O91" s="2"/>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>11</v>
       </c>
@@ -8862,9 +8775,8 @@
       <c r="K92" t="s">
         <v>13</v>
       </c>
-      <c r="O92" s="2"/>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>11</v>
       </c>
@@ -8898,9 +8810,8 @@
       <c r="K93" t="s">
         <v>13</v>
       </c>
-      <c r="O93" s="2"/>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>11</v>
       </c>
@@ -8934,9 +8845,8 @@
       <c r="K94" t="s">
         <v>13</v>
       </c>
-      <c r="O94" s="2"/>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>11</v>
       </c>
@@ -8970,9 +8880,8 @@
       <c r="K95" t="s">
         <v>13</v>
       </c>
-      <c r="O95" s="2"/>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>11</v>
       </c>
@@ -9006,9 +8915,8 @@
       <c r="K96" t="s">
         <v>13</v>
       </c>
-      <c r="O96" s="2"/>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>11</v>
       </c>
@@ -9042,9 +8950,8 @@
       <c r="K97" t="s">
         <v>13</v>
       </c>
-      <c r="O97" s="2"/>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>11</v>
       </c>
@@ -9078,9 +8985,8 @@
       <c r="K98" t="s">
         <v>13</v>
       </c>
-      <c r="O98" s="2"/>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>11</v>
       </c>
@@ -9114,9 +9020,8 @@
       <c r="K99" t="s">
         <v>13</v>
       </c>
-      <c r="O99" s="2"/>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>11</v>
       </c>
@@ -9150,9 +9055,8 @@
       <c r="K100" t="s">
         <v>13</v>
       </c>
-      <c r="O100" s="2"/>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>11</v>
       </c>
@@ -9186,9 +9090,8 @@
       <c r="K101" t="s">
         <v>13</v>
       </c>
-      <c r="O101" s="2"/>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>11</v>
       </c>
@@ -9222,9 +9125,8 @@
       <c r="K102" t="s">
         <v>13</v>
       </c>
-      <c r="O102" s="2"/>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>11</v>
       </c>
@@ -9258,9 +9160,8 @@
       <c r="K103" t="s">
         <v>13</v>
       </c>
-      <c r="O103" s="2"/>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>11</v>
       </c>
@@ -9294,9 +9195,8 @@
       <c r="K104" t="s">
         <v>13</v>
       </c>
-      <c r="O104" s="2"/>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>11</v>
       </c>
@@ -9330,9 +9230,8 @@
       <c r="K105" t="s">
         <v>13</v>
       </c>
-      <c r="O105" s="2"/>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>11</v>
       </c>
@@ -9366,9 +9265,8 @@
       <c r="K106" t="s">
         <v>13</v>
       </c>
-      <c r="O106" s="2"/>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>11</v>
       </c>
@@ -9402,9 +9300,8 @@
       <c r="K107" t="s">
         <v>13</v>
       </c>
-      <c r="O107" s="2"/>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>11</v>
       </c>
@@ -9438,9 +9335,8 @@
       <c r="K108" t="s">
         <v>13</v>
       </c>
-      <c r="O108" s="2"/>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>11</v>
       </c>
@@ -9474,9 +9370,8 @@
       <c r="K109" t="s">
         <v>13</v>
       </c>
-      <c r="O109" s="2"/>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>11</v>
       </c>
@@ -9510,9 +9405,8 @@
       <c r="K110" t="s">
         <v>13</v>
       </c>
-      <c r="O110" s="2"/>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>11</v>
       </c>
@@ -9546,9 +9440,8 @@
       <c r="K111" t="s">
         <v>13</v>
       </c>
-      <c r="O111" s="2"/>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>11</v>
       </c>
@@ -9582,7 +9475,6 @@
       <c r="K112" t="s">
         <v>13</v>
       </c>
-      <c r="O112" s="2"/>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
@@ -9618,7 +9510,6 @@
       <c r="K113" t="s">
         <v>13</v>
       </c>
-      <c r="O113" s="2"/>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
@@ -9654,7 +9545,6 @@
       <c r="K114" t="s">
         <v>13</v>
       </c>
-      <c r="O114" s="2"/>
     </row>
     <row r="115" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
@@ -9690,7 +9580,6 @@
       <c r="K115" t="s">
         <v>13</v>
       </c>
-      <c r="O115" s="2"/>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
@@ -9723,7 +9612,6 @@
       <c r="K116" t="s">
         <v>13</v>
       </c>
-      <c r="O116" s="2"/>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
@@ -9759,7 +9647,6 @@
       <c r="K117" t="s">
         <v>13</v>
       </c>
-      <c r="O117" s="2"/>
     </row>
     <row r="118" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
@@ -9795,7 +9682,6 @@
       <c r="K118" t="s">
         <v>13</v>
       </c>
-      <c r="O118" s="2"/>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
@@ -9831,7 +9717,6 @@
       <c r="K119" t="s">
         <v>13</v>
       </c>
-      <c r="O119" s="2"/>
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
@@ -9867,7 +9752,6 @@
       <c r="K120" t="s">
         <v>13</v>
       </c>
-      <c r="O120" s="2"/>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
@@ -9903,7 +9787,6 @@
       <c r="K121" t="s">
         <v>13</v>
       </c>
-      <c r="O121" s="2"/>
     </row>
     <row r="122" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
@@ -9939,7 +9822,6 @@
       <c r="K122" t="s">
         <v>13</v>
       </c>
-      <c r="O122" s="2"/>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
@@ -9975,7 +9857,6 @@
       <c r="K123" t="s">
         <v>13</v>
       </c>
-      <c r="O123" s="2"/>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
@@ -10011,7 +9892,7 @@
       <c r="K124" t="s">
         <v>13</v>
       </c>
-      <c r="O124" s="2" t="s">
+      <c r="O124" t="s">
         <v>1666</v>
       </c>
     </row>
@@ -10049,7 +9930,6 @@
       <c r="K125" t="s">
         <v>13</v>
       </c>
-      <c r="O125" s="2"/>
     </row>
     <row r="126" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
@@ -10085,7 +9965,6 @@
       <c r="K126" t="s">
         <v>13</v>
       </c>
-      <c r="O126" s="2"/>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
@@ -10121,7 +10000,6 @@
       <c r="K127" t="s">
         <v>13</v>
       </c>
-      <c r="O127" s="2"/>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
@@ -10157,9 +10035,8 @@
       <c r="K128" t="s">
         <v>13</v>
       </c>
-      <c r="O128" s="2"/>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>11</v>
       </c>
@@ -10193,9 +10070,8 @@
       <c r="K129" t="s">
         <v>13</v>
       </c>
-      <c r="O129" s="2"/>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>11</v>
       </c>
@@ -10229,9 +10105,8 @@
       <c r="K130" t="s">
         <v>13</v>
       </c>
-      <c r="O130" s="2"/>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>11</v>
       </c>
@@ -10265,9 +10140,8 @@
       <c r="K131" t="s">
         <v>13</v>
       </c>
-      <c r="O131" s="2"/>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>11</v>
       </c>
@@ -10301,9 +10175,8 @@
       <c r="K132" t="s">
         <v>13</v>
       </c>
-      <c r="O132" s="2"/>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>11</v>
       </c>
@@ -10337,9 +10210,8 @@
       <c r="K133" t="s">
         <v>13</v>
       </c>
-      <c r="O133" s="2"/>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>11</v>
       </c>
@@ -10373,9 +10245,8 @@
       <c r="K134" t="s">
         <v>13</v>
       </c>
-      <c r="O134" s="2"/>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>11</v>
       </c>
@@ -10409,9 +10280,8 @@
       <c r="K135" t="s">
         <v>13</v>
       </c>
-      <c r="O135" s="2"/>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>11</v>
       </c>
@@ -10445,9 +10315,8 @@
       <c r="K136" t="s">
         <v>13</v>
       </c>
-      <c r="O136" s="2"/>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>11</v>
       </c>
@@ -10481,9 +10350,8 @@
       <c r="K137" t="s">
         <v>13</v>
       </c>
-      <c r="O137" s="2"/>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>11</v>
       </c>
@@ -10517,9 +10385,8 @@
       <c r="K138" t="s">
         <v>13</v>
       </c>
-      <c r="O138" s="2"/>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>11</v>
       </c>
@@ -10553,9 +10420,8 @@
       <c r="K139" t="s">
         <v>13</v>
       </c>
-      <c r="O139" s="2"/>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>11</v>
       </c>
@@ -10589,9 +10455,8 @@
       <c r="K140" t="s">
         <v>13</v>
       </c>
-      <c r="O140" s="2"/>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>11</v>
       </c>
@@ -10625,9 +10490,8 @@
       <c r="K141" t="s">
         <v>13</v>
       </c>
-      <c r="O141" s="2"/>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>11</v>
       </c>
@@ -10661,9 +10525,8 @@
       <c r="K142" t="s">
         <v>13</v>
       </c>
-      <c r="O142" s="2"/>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>11</v>
       </c>
@@ -10697,9 +10560,8 @@
       <c r="K143" t="s">
         <v>13</v>
       </c>
-      <c r="O143" s="2"/>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>11</v>
       </c>
@@ -10733,9 +10595,8 @@
       <c r="K144" t="s">
         <v>13</v>
       </c>
-      <c r="O144" s="2"/>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>11</v>
       </c>
@@ -10769,9 +10630,8 @@
       <c r="K145" t="s">
         <v>13</v>
       </c>
-      <c r="O145" s="2"/>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>11</v>
       </c>
@@ -10805,9 +10665,8 @@
       <c r="K146" t="s">
         <v>13</v>
       </c>
-      <c r="O146" s="2"/>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>11</v>
       </c>
@@ -10841,9 +10700,8 @@
       <c r="K147" t="s">
         <v>13</v>
       </c>
-      <c r="O147" s="2"/>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>11</v>
       </c>
@@ -10877,9 +10735,8 @@
       <c r="K148" t="s">
         <v>13</v>
       </c>
-      <c r="O148" s="2"/>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>11</v>
       </c>
@@ -10913,9 +10770,8 @@
       <c r="K149" t="s">
         <v>13</v>
       </c>
-      <c r="O149" s="2"/>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>11</v>
       </c>
@@ -10949,9 +10805,8 @@
       <c r="K150" t="s">
         <v>13</v>
       </c>
-      <c r="O150" s="2"/>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>11</v>
       </c>
@@ -10985,9 +10840,8 @@
       <c r="K151" t="s">
         <v>13</v>
       </c>
-      <c r="O151" s="2"/>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>11</v>
       </c>
@@ -11021,9 +10875,8 @@
       <c r="K152" t="s">
         <v>13</v>
       </c>
-      <c r="O152" s="2"/>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>11</v>
       </c>
@@ -11057,9 +10910,8 @@
       <c r="K153" t="s">
         <v>13</v>
       </c>
-      <c r="O153" s="2"/>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>11</v>
       </c>
@@ -11093,9 +10945,8 @@
       <c r="K154" t="s">
         <v>13</v>
       </c>
-      <c r="O154" s="2"/>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>11</v>
       </c>
@@ -11129,9 +10980,8 @@
       <c r="K155" t="s">
         <v>13</v>
       </c>
-      <c r="O155" s="2"/>
-    </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>11</v>
       </c>
@@ -11165,9 +11015,8 @@
       <c r="K156" t="s">
         <v>13</v>
       </c>
-      <c r="O156" s="2"/>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>11</v>
       </c>
@@ -11201,9 +11050,8 @@
       <c r="K157" t="s">
         <v>13</v>
       </c>
-      <c r="O157" s="2"/>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>11</v>
       </c>
@@ -11237,9 +11085,8 @@
       <c r="K158" t="s">
         <v>13</v>
       </c>
-      <c r="O158" s="2"/>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>11</v>
       </c>
@@ -11273,9 +11120,8 @@
       <c r="K159" t="s">
         <v>13</v>
       </c>
-      <c r="O159" s="2"/>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>11</v>
       </c>
@@ -11309,9 +11155,8 @@
       <c r="K160" t="s">
         <v>13</v>
       </c>
-      <c r="O160" s="2"/>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>98</v>
       </c>
@@ -11345,9 +11190,8 @@
       <c r="K161" t="s">
         <v>13</v>
       </c>
-      <c r="O161" s="2"/>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>11</v>
       </c>
@@ -11381,9 +11225,8 @@
       <c r="K162" t="s">
         <v>13</v>
       </c>
-      <c r="O162" s="2"/>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>11</v>
       </c>
@@ -11417,9 +11260,8 @@
       <c r="K163" t="s">
         <v>13</v>
       </c>
-      <c r="O163" s="2"/>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>11</v>
       </c>
@@ -11453,9 +11295,8 @@
       <c r="K164" t="s">
         <v>13</v>
       </c>
-      <c r="O164" s="2"/>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>11</v>
       </c>
@@ -11489,9 +11330,8 @@
       <c r="K165" t="s">
         <v>13</v>
       </c>
-      <c r="O165" s="2"/>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>11</v>
       </c>
@@ -11525,9 +11365,8 @@
       <c r="K166" t="s">
         <v>13</v>
       </c>
-      <c r="O166" s="2"/>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>11</v>
       </c>
@@ -11561,9 +11400,8 @@
       <c r="K167" t="s">
         <v>13</v>
       </c>
-      <c r="O167" s="2"/>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>11</v>
       </c>
@@ -11597,9 +11435,8 @@
       <c r="K168" t="s">
         <v>13</v>
       </c>
-      <c r="O168" s="2"/>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>11</v>
       </c>
@@ -11633,9 +11470,8 @@
       <c r="K169" t="s">
         <v>13</v>
       </c>
-      <c r="O169" s="2"/>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>11</v>
       </c>
@@ -11669,9 +11505,8 @@
       <c r="K170" t="s">
         <v>13</v>
       </c>
-      <c r="O170" s="2"/>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>11</v>
       </c>
@@ -11705,9 +11540,8 @@
       <c r="K171" t="s">
         <v>13</v>
       </c>
-      <c r="O171" s="2"/>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>11</v>
       </c>
@@ -11741,9 +11575,8 @@
       <c r="K172" t="s">
         <v>13</v>
       </c>
-      <c r="O172" s="2"/>
-    </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>11</v>
       </c>
@@ -11777,9 +11610,8 @@
       <c r="K173" t="s">
         <v>13</v>
       </c>
-      <c r="O173" s="2"/>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>11</v>
       </c>
@@ -11813,9 +11645,8 @@
       <c r="K174" t="s">
         <v>13</v>
       </c>
-      <c r="O174" s="2"/>
-    </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>11</v>
       </c>
@@ -11849,9 +11680,8 @@
       <c r="K175" t="s">
         <v>13</v>
       </c>
-      <c r="O175" s="2"/>
-    </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>11</v>
       </c>
@@ -11885,9 +11715,8 @@
       <c r="K176" t="s">
         <v>13</v>
       </c>
-      <c r="O176" s="2"/>
-    </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>11</v>
       </c>
@@ -11921,9 +11750,8 @@
       <c r="K177" t="s">
         <v>13</v>
       </c>
-      <c r="O177" s="2"/>
-    </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>11</v>
       </c>
@@ -11957,9 +11785,8 @@
       <c r="K178" t="s">
         <v>13</v>
       </c>
-      <c r="O178" s="2"/>
-    </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>11</v>
       </c>
@@ -11993,9 +11820,8 @@
       <c r="K179" t="s">
         <v>13</v>
       </c>
-      <c r="O179" s="2"/>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>11</v>
       </c>
@@ -12029,9 +11855,8 @@
       <c r="K180" t="s">
         <v>13</v>
       </c>
-      <c r="O180" s="2"/>
-    </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>98</v>
       </c>
@@ -12065,9 +11890,8 @@
       <c r="K181" t="s">
         <v>13</v>
       </c>
-      <c r="O181" s="2"/>
-    </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>11</v>
       </c>
@@ -12101,9 +11925,8 @@
       <c r="K182" t="s">
         <v>13</v>
       </c>
-      <c r="O182" s="2"/>
-    </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>11</v>
       </c>
@@ -12137,9 +11960,8 @@
       <c r="K183" t="s">
         <v>13</v>
       </c>
-      <c r="O183" s="2"/>
-    </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>11</v>
       </c>
@@ -12173,9 +11995,8 @@
       <c r="K184" t="s">
         <v>13</v>
       </c>
-      <c r="O184" s="2"/>
-    </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>11</v>
       </c>
@@ -12209,9 +12030,8 @@
       <c r="K185" t="s">
         <v>13</v>
       </c>
-      <c r="O185" s="2"/>
-    </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>11</v>
       </c>
@@ -12245,9 +12065,8 @@
       <c r="K186" t="s">
         <v>13</v>
       </c>
-      <c r="O186" s="2"/>
-    </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>11</v>
       </c>
@@ -12281,9 +12100,8 @@
       <c r="K187" t="s">
         <v>13</v>
       </c>
-      <c r="O187" s="2"/>
-    </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>11</v>
       </c>
@@ -12317,9 +12135,8 @@
       <c r="K188" t="s">
         <v>13</v>
       </c>
-      <c r="O188" s="2"/>
-    </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>11</v>
       </c>
@@ -12353,9 +12170,8 @@
       <c r="K189" t="s">
         <v>13</v>
       </c>
-      <c r="O189" s="2"/>
-    </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>98</v>
       </c>
@@ -12389,9 +12205,8 @@
       <c r="K190" t="s">
         <v>13</v>
       </c>
-      <c r="O190" s="2"/>
-    </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>11</v>
       </c>
@@ -12425,9 +12240,8 @@
       <c r="K191" t="s">
         <v>13</v>
       </c>
-      <c r="O191" s="2"/>
-    </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>11</v>
       </c>
@@ -12461,9 +12275,8 @@
       <c r="K192" t="s">
         <v>13</v>
       </c>
-      <c r="O192" s="2"/>
-    </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>11</v>
       </c>
@@ -12497,9 +12310,8 @@
       <c r="K193" t="s">
         <v>13</v>
       </c>
-      <c r="O193" s="2"/>
-    </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>11</v>
       </c>
@@ -12533,9 +12345,8 @@
       <c r="K194" t="s">
         <v>390</v>
       </c>
-      <c r="O194" s="2"/>
-    </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>11</v>
       </c>
@@ -12569,9 +12380,8 @@
       <c r="K195" t="s">
         <v>13</v>
       </c>
-      <c r="O195" s="2"/>
-    </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>11</v>
       </c>
@@ -12605,9 +12415,8 @@
       <c r="K196" t="s">
         <v>13</v>
       </c>
-      <c r="O196" s="2"/>
-    </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>11</v>
       </c>
@@ -12641,9 +12450,8 @@
       <c r="K197" t="s">
         <v>13</v>
       </c>
-      <c r="O197" s="2"/>
-    </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>11</v>
       </c>
@@ -12677,9 +12485,8 @@
       <c r="K198" t="s">
         <v>13</v>
       </c>
-      <c r="O198" s="2"/>
-    </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>11</v>
       </c>
@@ -12713,9 +12520,8 @@
       <c r="K199" t="s">
         <v>13</v>
       </c>
-      <c r="O199" s="2"/>
-    </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>11</v>
       </c>
@@ -12749,9 +12555,8 @@
       <c r="K200" t="s">
         <v>13</v>
       </c>
-      <c r="O200" s="2"/>
-    </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>11</v>
       </c>
@@ -12785,9 +12590,8 @@
       <c r="K201" t="s">
         <v>13</v>
       </c>
-      <c r="O201" s="2"/>
-    </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>11</v>
       </c>
@@ -12821,9 +12625,8 @@
       <c r="K202" t="s">
         <v>13</v>
       </c>
-      <c r="O202" s="2"/>
-    </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>11</v>
       </c>
@@ -12857,9 +12660,8 @@
       <c r="K203" t="s">
         <v>13</v>
       </c>
-      <c r="O203" s="2"/>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>11</v>
       </c>
@@ -12893,9 +12695,8 @@
       <c r="K204" t="s">
         <v>13</v>
       </c>
-      <c r="O204" s="2"/>
-    </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>11</v>
       </c>
@@ -12929,9 +12730,8 @@
       <c r="K205" t="s">
         <v>13</v>
       </c>
-      <c r="O205" s="2"/>
-    </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>11</v>
       </c>
@@ -12965,9 +12765,8 @@
       <c r="K206" t="s">
         <v>13</v>
       </c>
-      <c r="O206" s="2"/>
-    </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>11</v>
       </c>
@@ -13001,9 +12800,8 @@
       <c r="K207" t="s">
         <v>13</v>
       </c>
-      <c r="O207" s="2"/>
-    </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>11</v>
       </c>
@@ -13037,9 +12835,8 @@
       <c r="K208" t="s">
         <v>13</v>
       </c>
-      <c r="O208" s="2"/>
-    </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>11</v>
       </c>
@@ -13073,9 +12870,8 @@
       <c r="K209" t="s">
         <v>13</v>
       </c>
-      <c r="O209" s="2"/>
-    </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>11</v>
       </c>
@@ -13109,9 +12905,8 @@
       <c r="K210" t="s">
         <v>13</v>
       </c>
-      <c r="O210" s="2"/>
-    </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>11</v>
       </c>
@@ -13145,9 +12940,8 @@
       <c r="K211" t="s">
         <v>13</v>
       </c>
-      <c r="O211" s="2"/>
-    </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>11</v>
       </c>
@@ -13181,9 +12975,8 @@
       <c r="K212" t="s">
         <v>13</v>
       </c>
-      <c r="O212" s="2"/>
-    </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>11</v>
       </c>
@@ -13217,9 +13010,8 @@
       <c r="K213" t="s">
         <v>13</v>
       </c>
-      <c r="O213" s="2"/>
-    </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>11</v>
       </c>
@@ -13253,9 +13045,8 @@
       <c r="K214" t="s">
         <v>13</v>
       </c>
-      <c r="O214" s="2"/>
-    </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>98</v>
       </c>
@@ -13289,9 +13080,8 @@
       <c r="K215" t="s">
         <v>13</v>
       </c>
-      <c r="O215" s="2"/>
-    </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>11</v>
       </c>
@@ -13325,9 +13115,8 @@
       <c r="K216" t="s">
         <v>13</v>
       </c>
-      <c r="O216" s="2"/>
-    </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>11</v>
       </c>
@@ -13361,9 +13150,8 @@
       <c r="K217" t="s">
         <v>13</v>
       </c>
-      <c r="O217" s="2"/>
-    </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>11</v>
       </c>
@@ -13397,9 +13185,8 @@
       <c r="K218" t="s">
         <v>13</v>
       </c>
-      <c r="O218" s="2"/>
-    </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>11</v>
       </c>
@@ -13433,9 +13220,8 @@
       <c r="K219" t="s">
         <v>13</v>
       </c>
-      <c r="O219" s="2"/>
-    </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>11</v>
       </c>
@@ -13469,9 +13255,8 @@
       <c r="K220" t="s">
         <v>13</v>
       </c>
-      <c r="O220" s="2"/>
-    </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>11</v>
       </c>
@@ -13505,9 +13290,8 @@
       <c r="K221" t="s">
         <v>13</v>
       </c>
-      <c r="O221" s="2"/>
-    </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>98</v>
       </c>
@@ -13541,9 +13325,8 @@
       <c r="K222" t="s">
         <v>13</v>
       </c>
-      <c r="O222" s="2"/>
-    </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>11</v>
       </c>
@@ -13577,9 +13360,8 @@
       <c r="K223" t="s">
         <v>13</v>
       </c>
-      <c r="O223" s="2"/>
-    </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>11</v>
       </c>
@@ -13613,7 +13395,6 @@
       <c r="K224" t="s">
         <v>13</v>
       </c>
-      <c r="O224" s="2"/>
     </row>
     <row r="225" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
@@ -13649,7 +13430,6 @@
       <c r="K225" t="s">
         <v>13</v>
       </c>
-      <c r="O225" s="2"/>
     </row>
     <row r="226" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
@@ -13685,7 +13465,6 @@
       <c r="K226" t="s">
         <v>13</v>
       </c>
-      <c r="O226" s="2"/>
     </row>
     <row r="227" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
@@ -13721,7 +13500,6 @@
       <c r="K227" t="s">
         <v>13</v>
       </c>
-      <c r="O227" s="2"/>
     </row>
     <row r="228" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
@@ -13757,7 +13535,6 @@
       <c r="K228" t="s">
         <v>13</v>
       </c>
-      <c r="O228" s="2"/>
     </row>
     <row r="229" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
@@ -13793,7 +13570,6 @@
       <c r="K229" t="s">
         <v>13</v>
       </c>
-      <c r="O229" s="2"/>
     </row>
     <row r="230" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
@@ -13829,7 +13605,6 @@
       <c r="K230" t="s">
         <v>13</v>
       </c>
-      <c r="O230" s="2"/>
     </row>
     <row r="231" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
@@ -13865,7 +13640,6 @@
       <c r="K231" t="s">
         <v>13</v>
       </c>
-      <c r="O231" s="2"/>
     </row>
     <row r="232" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A232" t="s">
@@ -13901,7 +13675,6 @@
       <c r="K232" t="s">
         <v>13</v>
       </c>
-      <c r="O232" s="2"/>
     </row>
     <row r="233" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A233" t="s">
@@ -13937,7 +13710,6 @@
       <c r="K233" t="s">
         <v>13</v>
       </c>
-      <c r="O233" s="2"/>
     </row>
     <row r="234" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A234" t="s">
@@ -13973,7 +13745,6 @@
       <c r="K234" t="s">
         <v>13</v>
       </c>
-      <c r="O234" s="2"/>
     </row>
     <row r="235" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A235" t="s">
@@ -14009,7 +13780,6 @@
       <c r="K235" t="s">
         <v>13</v>
       </c>
-      <c r="O235" s="2"/>
     </row>
     <row r="236" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A236" t="s">
@@ -14045,7 +13815,7 @@
       <c r="K236" t="s">
         <v>13</v>
       </c>
-      <c r="O236" s="2" t="s">
+      <c r="O236" t="s">
         <v>1665</v>
       </c>
     </row>
@@ -14083,7 +13853,6 @@
       <c r="K237" t="s">
         <v>13</v>
       </c>
-      <c r="O237" s="2"/>
     </row>
     <row r="238" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A238" t="s">
@@ -14119,7 +13888,6 @@
       <c r="K238" t="s">
         <v>13</v>
       </c>
-      <c r="O238" s="2"/>
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A239" t="s">
@@ -14155,7 +13923,6 @@
       <c r="K239" t="s">
         <v>13</v>
       </c>
-      <c r="O239" s="2"/>
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A240" t="s">
@@ -14191,9 +13958,8 @@
       <c r="K240" t="s">
         <v>13</v>
       </c>
-      <c r="O240" s="2"/>
-    </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>11</v>
       </c>
@@ -14227,9 +13993,8 @@
       <c r="K241" t="s">
         <v>13</v>
       </c>
-      <c r="O241" s="2"/>
-    </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
         <v>11</v>
       </c>
@@ -14263,9 +14028,8 @@
       <c r="K242" t="s">
         <v>13</v>
       </c>
-      <c r="O242" s="2"/>
-    </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
         <v>11</v>
       </c>
@@ -14299,9 +14063,8 @@
       <c r="K243" t="s">
         <v>13</v>
       </c>
-      <c r="O243" s="2"/>
-    </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
         <v>11</v>
       </c>
@@ -14335,9 +14098,8 @@
       <c r="K244" t="s">
         <v>13</v>
       </c>
-      <c r="O244" s="2"/>
-    </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
         <v>11</v>
       </c>
@@ -14371,9 +14133,8 @@
       <c r="K245" t="s">
         <v>13</v>
       </c>
-      <c r="O245" s="2"/>
-    </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
         <v>11</v>
       </c>
@@ -14407,9 +14168,8 @@
       <c r="K246" t="s">
         <v>13</v>
       </c>
-      <c r="O246" s="2"/>
-    </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
         <v>11</v>
       </c>
@@ -14443,9 +14203,8 @@
       <c r="K247" t="s">
         <v>13</v>
       </c>
-      <c r="O247" s="2"/>
-    </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
         <v>11</v>
       </c>
@@ -14479,9 +14238,8 @@
       <c r="K248" t="s">
         <v>13</v>
       </c>
-      <c r="O248" s="2"/>
-    </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A249" t="s">
         <v>11</v>
       </c>
@@ -14515,9 +14273,8 @@
       <c r="K249" t="s">
         <v>13</v>
       </c>
-      <c r="O249" s="2"/>
-    </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
         <v>11</v>
       </c>
@@ -14551,9 +14308,8 @@
       <c r="K250" t="s">
         <v>13</v>
       </c>
-      <c r="O250" s="2"/>
-    </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A251" t="s">
         <v>11</v>
       </c>
@@ -14587,9 +14343,8 @@
       <c r="K251" t="s">
         <v>13</v>
       </c>
-      <c r="O251" s="2"/>
-    </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A252" t="s">
         <v>11</v>
       </c>
@@ -14623,9 +14378,8 @@
       <c r="K252" t="s">
         <v>13</v>
       </c>
-      <c r="O252" s="2"/>
-    </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>11</v>
       </c>
@@ -14659,9 +14413,8 @@
       <c r="K253" t="s">
         <v>13</v>
       </c>
-      <c r="O253" s="2"/>
-    </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A254" t="s">
         <v>11</v>
       </c>
@@ -14695,9 +14448,8 @@
       <c r="K254" t="s">
         <v>13</v>
       </c>
-      <c r="O254" s="2"/>
-    </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A255" t="s">
         <v>11</v>
       </c>
@@ -14731,9 +14483,8 @@
       <c r="K255" t="s">
         <v>13</v>
       </c>
-      <c r="O255" s="2"/>
-    </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A256" t="s">
         <v>11</v>
       </c>
@@ -14767,9 +14518,8 @@
       <c r="K256" t="s">
         <v>13</v>
       </c>
-      <c r="O256" s="2"/>
-    </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A257" t="s">
         <v>11</v>
       </c>
@@ -14803,9 +14553,8 @@
       <c r="K257" t="s">
         <v>13</v>
       </c>
-      <c r="O257" s="2"/>
-    </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A258" t="s">
         <v>11</v>
       </c>
@@ -14839,9 +14588,8 @@
       <c r="K258" t="s">
         <v>13</v>
       </c>
-      <c r="O258" s="2"/>
-    </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A259" t="s">
         <v>11</v>
       </c>
@@ -14875,9 +14623,8 @@
       <c r="K259" t="s">
         <v>13</v>
       </c>
-      <c r="O259" s="2"/>
-    </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A260" t="s">
         <v>11</v>
       </c>
@@ -14911,9 +14658,8 @@
       <c r="K260" t="s">
         <v>13</v>
       </c>
-      <c r="O260" s="2"/>
-    </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A261" t="s">
         <v>11</v>
       </c>
@@ -14947,9 +14693,8 @@
       <c r="K261" t="s">
         <v>13</v>
       </c>
-      <c r="O261" s="2"/>
-    </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A262" t="s">
         <v>11</v>
       </c>
@@ -14983,9 +14728,8 @@
       <c r="K262" t="s">
         <v>13</v>
       </c>
-      <c r="O262" s="2"/>
-    </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A263" t="s">
         <v>11</v>
       </c>
@@ -15019,9 +14763,8 @@
       <c r="K263" t="s">
         <v>13</v>
       </c>
-      <c r="O263" s="2"/>
-    </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A264" t="s">
         <v>11</v>
       </c>
@@ -15055,9 +14798,8 @@
       <c r="K264" t="s">
         <v>13</v>
       </c>
-      <c r="O264" s="2"/>
-    </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A265" t="s">
         <v>11</v>
       </c>
@@ -15091,9 +14833,8 @@
       <c r="K265" t="s">
         <v>13</v>
       </c>
-      <c r="O265" s="2"/>
-    </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A266" t="s">
         <v>11</v>
       </c>
@@ -15127,9 +14868,8 @@
       <c r="K266" t="s">
         <v>13</v>
       </c>
-      <c r="O266" s="2"/>
-    </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A267" t="s">
         <v>11</v>
       </c>
@@ -15163,9 +14903,8 @@
       <c r="K267" t="s">
         <v>13</v>
       </c>
-      <c r="O267" s="2"/>
-    </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A268" t="s">
         <v>98</v>
       </c>
@@ -15199,9 +14938,8 @@
       <c r="K268" t="s">
         <v>13</v>
       </c>
-      <c r="O268" s="2"/>
-    </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
         <v>98</v>
       </c>
@@ -15235,9 +14973,8 @@
       <c r="K269" t="s">
         <v>13</v>
       </c>
-      <c r="O269" s="2"/>
-    </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A270" t="s">
         <v>11</v>
       </c>
@@ -15271,9 +15008,8 @@
       <c r="K270" t="s">
         <v>13</v>
       </c>
-      <c r="O270" s="2"/>
-    </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A271" t="s">
         <v>11</v>
       </c>
@@ -15307,9 +15043,8 @@
       <c r="K271" t="s">
         <v>13</v>
       </c>
-      <c r="O271" s="2"/>
-    </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A272" t="s">
         <v>11</v>
       </c>
@@ -15343,7 +15078,6 @@
       <c r="K272" t="s">
         <v>13</v>
       </c>
-      <c r="O272" s="2"/>
     </row>
     <row r="273" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
@@ -15379,7 +15113,6 @@
       <c r="K273" t="s">
         <v>13</v>
       </c>
-      <c r="O273" s="2"/>
     </row>
     <row r="274" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
@@ -15415,7 +15148,6 @@
       <c r="K274" t="s">
         <v>13</v>
       </c>
-      <c r="O274" s="2"/>
     </row>
     <row r="275" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
@@ -15451,7 +15183,6 @@
       <c r="K275" t="s">
         <v>13</v>
       </c>
-      <c r="O275" s="2"/>
     </row>
     <row r="276" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A276" t="s">
@@ -15487,7 +15218,6 @@
       <c r="K276" t="s">
         <v>13</v>
       </c>
-      <c r="O276" s="2"/>
     </row>
     <row r="277" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A277" t="s">
@@ -15523,7 +15253,6 @@
       <c r="K277" t="s">
         <v>13</v>
       </c>
-      <c r="O277" s="2"/>
     </row>
     <row r="278" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A278" t="s">
@@ -15559,7 +15288,6 @@
       <c r="K278" t="s">
         <v>13</v>
       </c>
-      <c r="O278" s="2"/>
     </row>
     <row r="279" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A279" t="s">
@@ -15595,7 +15323,7 @@
       <c r="K279" t="s">
         <v>13</v>
       </c>
-      <c r="O279" s="2" t="s">
+      <c r="O279" t="s">
         <v>1662</v>
       </c>
     </row>
@@ -15633,7 +15361,6 @@
       <c r="K280" t="s">
         <v>13</v>
       </c>
-      <c r="O280" s="2"/>
     </row>
     <row r="281" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A281" t="s">
@@ -15669,7 +15396,6 @@
       <c r="K281" t="s">
         <v>13</v>
       </c>
-      <c r="O281" s="2"/>
     </row>
     <row r="282" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A282" t="s">
@@ -15705,7 +15431,6 @@
       <c r="K282" t="s">
         <v>13</v>
       </c>
-      <c r="O282" s="2"/>
     </row>
     <row r="283" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A283" t="s">
@@ -15741,7 +15466,6 @@
       <c r="K283" t="s">
         <v>13</v>
       </c>
-      <c r="O283" s="2"/>
     </row>
     <row r="284" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A284" t="s">
@@ -15777,7 +15501,6 @@
       <c r="K284" t="s">
         <v>13</v>
       </c>
-      <c r="O284" s="2"/>
     </row>
     <row r="285" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A285" t="s">
@@ -15813,7 +15536,6 @@
       <c r="K285" t="s">
         <v>13</v>
       </c>
-      <c r="O285" s="2"/>
     </row>
     <row r="286" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A286" t="s">
@@ -15849,7 +15571,6 @@
       <c r="K286" t="s">
         <v>13</v>
       </c>
-      <c r="O286" s="2"/>
     </row>
     <row r="287" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A287" t="s">
@@ -15885,7 +15606,6 @@
       <c r="K287" t="s">
         <v>13</v>
       </c>
-      <c r="O287" s="2"/>
     </row>
     <row r="288" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A288" t="s">
@@ -15921,9 +15641,8 @@
       <c r="K288" t="s">
         <v>13</v>
       </c>
-      <c r="O288" s="2"/>
-    </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A289" t="s">
         <v>11</v>
       </c>
@@ -15957,9 +15676,8 @@
       <c r="K289" t="s">
         <v>13</v>
       </c>
-      <c r="O289" s="2"/>
-    </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A290" t="s">
         <v>11</v>
       </c>
@@ -15993,9 +15711,8 @@
       <c r="K290" t="s">
         <v>13</v>
       </c>
-      <c r="O290" s="2"/>
-    </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A291" t="s">
         <v>11</v>
       </c>
@@ -16029,9 +15746,8 @@
       <c r="K291" t="s">
         <v>13</v>
       </c>
-      <c r="O291" s="2"/>
-    </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A292" t="s">
         <v>11</v>
       </c>
@@ -16065,9 +15781,8 @@
       <c r="K292" t="s">
         <v>13</v>
       </c>
-      <c r="O292" s="2"/>
-    </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A293" t="s">
         <v>11</v>
       </c>
@@ -16101,9 +15816,8 @@
       <c r="K293" t="s">
         <v>13</v>
       </c>
-      <c r="O293" s="2"/>
-    </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="294" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A294" t="s">
         <v>11</v>
       </c>
@@ -16137,9 +15851,8 @@
       <c r="K294" t="s">
         <v>13</v>
       </c>
-      <c r="O294" s="2"/>
-    </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="295" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A295" t="s">
         <v>11</v>
       </c>
@@ -16173,9 +15886,8 @@
       <c r="K295" t="s">
         <v>13</v>
       </c>
-      <c r="O295" s="2"/>
-    </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="296" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A296" t="s">
         <v>11</v>
       </c>
@@ -16209,9 +15921,8 @@
       <c r="K296" t="s">
         <v>13</v>
       </c>
-      <c r="O296" s="2"/>
-    </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A297" t="s">
         <v>11</v>
       </c>
@@ -16245,9 +15956,8 @@
       <c r="K297" t="s">
         <v>13</v>
       </c>
-      <c r="O297" s="2"/>
-    </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A298" t="s">
         <v>11</v>
       </c>
@@ -16281,9 +15991,8 @@
       <c r="K298" t="s">
         <v>13</v>
       </c>
-      <c r="O298" s="2"/>
-    </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A299" t="s">
         <v>11</v>
       </c>
@@ -16317,9 +16026,8 @@
       <c r="K299" t="s">
         <v>13</v>
       </c>
-      <c r="O299" s="2"/>
-    </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="300" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A300" t="s">
         <v>11</v>
       </c>
@@ -16353,9 +16061,8 @@
       <c r="K300" t="s">
         <v>13</v>
       </c>
-      <c r="O300" s="2"/>
-    </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="301" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A301" t="s">
         <v>11</v>
       </c>
@@ -16389,9 +16096,8 @@
       <c r="K301" t="s">
         <v>13</v>
       </c>
-      <c r="O301" s="2"/>
-    </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A302" t="s">
         <v>11</v>
       </c>
@@ -16425,9 +16131,8 @@
       <c r="K302" t="s">
         <v>13</v>
       </c>
-      <c r="O302" s="2"/>
-    </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A303" t="s">
         <v>11</v>
       </c>
@@ -16461,9 +16166,8 @@
       <c r="K303" t="s">
         <v>13</v>
       </c>
-      <c r="O303" s="2"/>
-    </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A304" t="s">
         <v>11</v>
       </c>
@@ -16497,9 +16201,8 @@
       <c r="K304" t="s">
         <v>13</v>
       </c>
-      <c r="O304" s="2"/>
-    </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A305" t="s">
         <v>11</v>
       </c>
@@ -16533,9 +16236,8 @@
       <c r="K305" t="s">
         <v>13</v>
       </c>
-      <c r="O305" s="2"/>
-    </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
         <v>11</v>
       </c>
@@ -16569,9 +16271,8 @@
       <c r="K306" t="s">
         <v>13</v>
       </c>
-      <c r="O306" s="2"/>
-    </row>
-    <row r="307" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
         <v>11</v>
       </c>
@@ -16605,9 +16306,8 @@
       <c r="K307" t="s">
         <v>13</v>
       </c>
-      <c r="O307" s="2"/>
-    </row>
-    <row r="308" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
         <v>11</v>
       </c>
@@ -16641,9 +16341,8 @@
       <c r="K308" t="s">
         <v>13</v>
       </c>
-      <c r="O308" s="2"/>
-    </row>
-    <row r="309" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
         <v>11</v>
       </c>
@@ -16677,9 +16376,8 @@
       <c r="K309" t="s">
         <v>13</v>
       </c>
-      <c r="O309" s="2"/>
-    </row>
-    <row r="310" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
         <v>11</v>
       </c>
@@ -16713,9 +16411,8 @@
       <c r="K310" t="s">
         <v>13</v>
       </c>
-      <c r="O310" s="2"/>
-    </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
         <v>11</v>
       </c>
@@ -16749,9 +16446,8 @@
       <c r="K311" t="s">
         <v>13</v>
       </c>
-      <c r="O311" s="2"/>
-    </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
         <v>11</v>
       </c>
@@ -16785,9 +16481,8 @@
       <c r="K312" t="s">
         <v>13</v>
       </c>
-      <c r="O312" s="2"/>
-    </row>
-    <row r="313" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
         <v>11</v>
       </c>
@@ -16821,9 +16516,8 @@
       <c r="K313" t="s">
         <v>13</v>
       </c>
-      <c r="O313" s="2"/>
-    </row>
-    <row r="314" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A314" t="s">
         <v>11</v>
       </c>
@@ -16857,9 +16551,8 @@
       <c r="K314" t="s">
         <v>13</v>
       </c>
-      <c r="O314" s="2"/>
-    </row>
-    <row r="315" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
         <v>11</v>
       </c>
@@ -16893,9 +16586,8 @@
       <c r="K315" t="s">
         <v>13</v>
       </c>
-      <c r="O315" s="2"/>
-    </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
         <v>11</v>
       </c>
@@ -16929,9 +16621,8 @@
       <c r="K316" t="s">
         <v>13</v>
       </c>
-      <c r="O316" s="2"/>
-    </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
         <v>11</v>
       </c>
@@ -16965,9 +16656,8 @@
       <c r="K317" t="s">
         <v>13</v>
       </c>
-      <c r="O317" s="2"/>
-    </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
         <v>11</v>
       </c>
@@ -17001,9 +16691,8 @@
       <c r="K318" t="s">
         <v>13</v>
       </c>
-      <c r="O318" s="2"/>
-    </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
         <v>11</v>
       </c>
@@ -17037,9 +16726,8 @@
       <c r="K319" t="s">
         <v>13</v>
       </c>
-      <c r="O319" s="2"/>
-    </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
         <v>11</v>
       </c>
@@ -17073,7 +16761,6 @@
       <c r="K320" t="s">
         <v>13</v>
       </c>
-      <c r="O320" s="2"/>
     </row>
     <row r="321" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
@@ -17109,7 +16796,6 @@
       <c r="K321" t="s">
         <v>682</v>
       </c>
-      <c r="O321" s="2"/>
     </row>
     <row r="322" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
@@ -17145,7 +16831,6 @@
       <c r="K322" t="s">
         <v>13</v>
       </c>
-      <c r="O322" s="2"/>
     </row>
     <row r="323" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
@@ -17181,7 +16866,6 @@
       <c r="K323" t="s">
         <v>13</v>
       </c>
-      <c r="O323" s="2"/>
     </row>
     <row r="324" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
@@ -17217,7 +16901,6 @@
       <c r="K324" t="s">
         <v>13</v>
       </c>
-      <c r="O324" s="2"/>
     </row>
     <row r="325" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
@@ -17253,7 +16936,6 @@
       <c r="K325" t="s">
         <v>13</v>
       </c>
-      <c r="O325" s="2"/>
     </row>
     <row r="326" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
@@ -17289,7 +16971,6 @@
       <c r="K326" t="s">
         <v>13</v>
       </c>
-      <c r="O326" s="2"/>
     </row>
     <row r="327" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
@@ -17325,7 +17006,6 @@
       <c r="K327" t="s">
         <v>13</v>
       </c>
-      <c r="O327" s="2"/>
     </row>
     <row r="328" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
@@ -17361,7 +17041,6 @@
       <c r="K328" t="s">
         <v>13</v>
       </c>
-      <c r="O328" s="2"/>
     </row>
     <row r="329" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
@@ -17397,7 +17076,6 @@
       <c r="K329" t="s">
         <v>13</v>
       </c>
-      <c r="O329" s="2"/>
     </row>
     <row r="330" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
@@ -17433,7 +17111,6 @@
       <c r="K330" t="s">
         <v>13</v>
       </c>
-      <c r="O330" s="2"/>
     </row>
     <row r="331" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
@@ -17469,7 +17146,6 @@
       <c r="K331" t="s">
         <v>13</v>
       </c>
-      <c r="O331" s="2"/>
     </row>
     <row r="332" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
@@ -17505,7 +17181,6 @@
       <c r="K332" t="s">
         <v>13</v>
       </c>
-      <c r="O332" s="2"/>
     </row>
     <row r="333" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
@@ -17541,7 +17216,6 @@
       <c r="K333" t="s">
         <v>13</v>
       </c>
-      <c r="O333" s="2"/>
     </row>
     <row r="334" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
@@ -17577,7 +17251,6 @@
       <c r="K334" t="s">
         <v>13</v>
       </c>
-      <c r="O334" s="2"/>
     </row>
     <row r="335" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
@@ -17651,9 +17324,8 @@
       <c r="K336" t="s">
         <v>13</v>
       </c>
-      <c r="O336" s="2"/>
-    </row>
-    <row r="337" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="337" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A337" t="s">
         <v>11</v>
       </c>
@@ -17687,9 +17359,8 @@
       <c r="K337" t="s">
         <v>13</v>
       </c>
-      <c r="O337" s="2"/>
-    </row>
-    <row r="338" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="338" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A338" t="s">
         <v>11</v>
       </c>
@@ -17723,9 +17394,8 @@
       <c r="K338" t="s">
         <v>13</v>
       </c>
-      <c r="O338" s="2"/>
-    </row>
-    <row r="339" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="339" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A339" t="s">
         <v>11</v>
       </c>
@@ -17759,9 +17429,8 @@
       <c r="K339" t="s">
         <v>13</v>
       </c>
-      <c r="O339" s="2"/>
-    </row>
-    <row r="340" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="340" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A340" t="s">
         <v>11</v>
       </c>
@@ -17795,9 +17464,8 @@
       <c r="K340" t="s">
         <v>13</v>
       </c>
-      <c r="O340" s="2"/>
-    </row>
-    <row r="341" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="341" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A341" t="s">
         <v>11</v>
       </c>
@@ -17831,9 +17499,8 @@
       <c r="K341" t="s">
         <v>13</v>
       </c>
-      <c r="O341" s="2"/>
-    </row>
-    <row r="342" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="342" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A342" t="s">
         <v>11</v>
       </c>
@@ -17867,9 +17534,8 @@
       <c r="K342" t="s">
         <v>13</v>
       </c>
-      <c r="O342" s="2"/>
-    </row>
-    <row r="343" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="343" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A343" t="s">
         <v>11</v>
       </c>
@@ -17903,9 +17569,8 @@
       <c r="K343" t="s">
         <v>13</v>
       </c>
-      <c r="O343" s="2"/>
-    </row>
-    <row r="344" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="344" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A344" t="s">
         <v>11</v>
       </c>
@@ -17939,9 +17604,8 @@
       <c r="K344" t="s">
         <v>13</v>
       </c>
-      <c r="O344" s="2"/>
-    </row>
-    <row r="345" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="345" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A345" t="s">
         <v>11</v>
       </c>
@@ -17975,9 +17639,8 @@
       <c r="K345" t="s">
         <v>13</v>
       </c>
-      <c r="O345" s="2"/>
-    </row>
-    <row r="346" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="346" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A346" t="s">
         <v>11</v>
       </c>
@@ -18011,9 +17674,8 @@
       <c r="K346" t="s">
         <v>13</v>
       </c>
-      <c r="O346" s="2"/>
-    </row>
-    <row r="347" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="347" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A347" t="s">
         <v>11</v>
       </c>
@@ -18047,9 +17709,8 @@
       <c r="K347" t="s">
         <v>13</v>
       </c>
-      <c r="O347" s="2"/>
-    </row>
-    <row r="348" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="348" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A348" t="s">
         <v>11</v>
       </c>
@@ -18083,9 +17744,8 @@
       <c r="K348" t="s">
         <v>13</v>
       </c>
-      <c r="O348" s="2"/>
-    </row>
-    <row r="349" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="349" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
         <v>11</v>
       </c>
@@ -18119,9 +17779,8 @@
       <c r="K349" t="s">
         <v>13</v>
       </c>
-      <c r="O349" s="2"/>
-    </row>
-    <row r="350" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="350" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
         <v>11</v>
       </c>
@@ -18155,9 +17814,8 @@
       <c r="K350" t="s">
         <v>13</v>
       </c>
-      <c r="O350" s="2"/>
-    </row>
-    <row r="351" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="351" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
         <v>11</v>
       </c>
@@ -18191,9 +17849,8 @@
       <c r="K351" t="s">
         <v>13</v>
       </c>
-      <c r="O351" s="2"/>
-    </row>
-    <row r="352" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="352" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
         <v>11</v>
       </c>
@@ -18227,9 +17884,8 @@
       <c r="K352" t="s">
         <v>13</v>
       </c>
-      <c r="O352" s="2"/>
-    </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="353" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
         <v>11</v>
       </c>
@@ -18263,9 +17919,8 @@
       <c r="K353" t="s">
         <v>13</v>
       </c>
-      <c r="O353" s="2"/>
-    </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="354" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
         <v>11</v>
       </c>
@@ -18299,9 +17954,8 @@
       <c r="K354" t="s">
         <v>13</v>
       </c>
-      <c r="O354" s="2"/>
-    </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="355" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
         <v>11</v>
       </c>
@@ -18335,9 +17989,8 @@
       <c r="K355" t="s">
         <v>13</v>
       </c>
-      <c r="O355" s="2"/>
-    </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="356" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
         <v>11</v>
       </c>
@@ -18371,9 +18024,8 @@
       <c r="K356" t="s">
         <v>13</v>
       </c>
-      <c r="O356" s="2"/>
-    </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="357" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A357" t="s">
         <v>11</v>
       </c>
@@ -18407,9 +18059,8 @@
       <c r="K357" t="s">
         <v>13</v>
       </c>
-      <c r="O357" s="2"/>
-    </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="358" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A358" t="s">
         <v>11</v>
       </c>
@@ -18443,9 +18094,8 @@
       <c r="K358" t="s">
         <v>13</v>
       </c>
-      <c r="O358" s="2"/>
-    </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="359" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A359" t="s">
         <v>11</v>
       </c>
@@ -18479,9 +18129,8 @@
       <c r="K359" t="s">
         <v>13</v>
       </c>
-      <c r="O359" s="2"/>
-    </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="360" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A360" t="s">
         <v>11</v>
       </c>
@@ -18515,9 +18164,8 @@
       <c r="K360" t="s">
         <v>13</v>
       </c>
-      <c r="O360" s="2"/>
-    </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="361" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A361" t="s">
         <v>11</v>
       </c>
@@ -18551,9 +18199,8 @@
       <c r="K361" t="s">
         <v>13</v>
       </c>
-      <c r="O361" s="2"/>
-    </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="362" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A362" t="s">
         <v>11</v>
       </c>
@@ -18587,9 +18234,8 @@
       <c r="K362" t="s">
         <v>13</v>
       </c>
-      <c r="O362" s="2"/>
-    </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="363" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A363" t="s">
         <v>11</v>
       </c>
@@ -18623,9 +18269,8 @@
       <c r="K363" t="s">
         <v>13</v>
       </c>
-      <c r="O363" s="2"/>
-    </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="364" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A364" t="s">
         <v>11</v>
       </c>
@@ -18659,9 +18304,8 @@
       <c r="K364" t="s">
         <v>13</v>
       </c>
-      <c r="O364" s="2"/>
-    </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="365" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A365" t="s">
         <v>11</v>
       </c>
@@ -18695,9 +18339,8 @@
       <c r="K365" t="s">
         <v>13</v>
       </c>
-      <c r="O365" s="2"/>
-    </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="366" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A366" t="s">
         <v>11</v>
       </c>
@@ -18731,9 +18374,8 @@
       <c r="K366" t="s">
         <v>13</v>
       </c>
-      <c r="O366" s="2"/>
-    </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="367" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A367" t="s">
         <v>11</v>
       </c>
@@ -18767,9 +18409,8 @@
       <c r="K367" t="s">
         <v>13</v>
       </c>
-      <c r="O367" s="2"/>
-    </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="368" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A368" t="s">
         <v>11</v>
       </c>
@@ -18803,7 +18444,6 @@
       <c r="K368" t="s">
         <v>13</v>
       </c>
-      <c r="O368" s="2"/>
     </row>
     <row r="369" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A369" t="s">
@@ -18839,7 +18479,6 @@
       <c r="K369" t="s">
         <v>13</v>
       </c>
-      <c r="O369" s="2"/>
     </row>
     <row r="370" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A370" t="s">
@@ -18875,7 +18514,6 @@
       <c r="K370" t="s">
         <v>13</v>
       </c>
-      <c r="O370" s="2"/>
     </row>
     <row r="371" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A371" t="s">
@@ -18911,7 +18549,6 @@
       <c r="K371" t="s">
         <v>13</v>
       </c>
-      <c r="O371" s="2"/>
     </row>
     <row r="372" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A372" t="s">
@@ -18947,7 +18584,6 @@
       <c r="K372" t="s">
         <v>13</v>
       </c>
-      <c r="O372" s="2"/>
     </row>
     <row r="373" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A373" t="s">
@@ -18983,7 +18619,6 @@
       <c r="K373" t="s">
         <v>13</v>
       </c>
-      <c r="O373" s="2"/>
     </row>
     <row r="374" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A374" t="s">
@@ -19019,7 +18654,6 @@
       <c r="K374" t="s">
         <v>13</v>
       </c>
-      <c r="O374" s="2"/>
     </row>
     <row r="375" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A375" t="s">
@@ -19055,7 +18689,6 @@
       <c r="K375" t="s">
         <v>13</v>
       </c>
-      <c r="O375" s="2"/>
     </row>
     <row r="376" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A376" t="s">
@@ -19091,7 +18724,6 @@
       <c r="K376" t="s">
         <v>13</v>
       </c>
-      <c r="O376" s="2"/>
     </row>
     <row r="377" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A377" t="s">
@@ -19127,7 +18759,7 @@
       <c r="K377" t="s">
         <v>13</v>
       </c>
-      <c r="O377" s="2" t="s">
+      <c r="O377" t="s">
         <v>1663</v>
       </c>
     </row>
@@ -19165,7 +18797,6 @@
       <c r="K378" t="s">
         <v>13</v>
       </c>
-      <c r="O378" s="2"/>
     </row>
     <row r="379" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A379" t="s">
@@ -19201,7 +18832,6 @@
       <c r="K379" t="s">
         <v>13</v>
       </c>
-      <c r="O379" s="2"/>
     </row>
     <row r="380" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A380" t="s">
@@ -19237,7 +18867,6 @@
       <c r="K380" t="s">
         <v>13</v>
       </c>
-      <c r="O380" s="2"/>
     </row>
     <row r="381" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A381" t="s">
@@ -19273,7 +18902,6 @@
       <c r="K381" t="s">
         <v>13</v>
       </c>
-      <c r="O381" s="2"/>
     </row>
     <row r="382" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A382" t="s">
@@ -19309,7 +18937,6 @@
       <c r="K382" t="s">
         <v>13</v>
       </c>
-      <c r="O382" s="2"/>
     </row>
     <row r="383" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A383" t="s">
@@ -19345,7 +18972,6 @@
       <c r="K383" t="s">
         <v>13</v>
       </c>
-      <c r="O383" s="2"/>
     </row>
     <row r="384" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A384" t="s">
@@ -19381,9 +19007,8 @@
       <c r="K384" t="s">
         <v>13</v>
       </c>
-      <c r="O384" s="2"/>
-    </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="385" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A385" t="s">
         <v>11</v>
       </c>
@@ -19417,9 +19042,8 @@
       <c r="K385" t="s">
         <v>13</v>
       </c>
-      <c r="O385" s="2"/>
-    </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="386" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A386" t="s">
         <v>11</v>
       </c>
@@ -19453,9 +19077,8 @@
       <c r="K386" t="s">
         <v>13</v>
       </c>
-      <c r="O386" s="2"/>
-    </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="387" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A387" t="s">
         <v>11</v>
       </c>
@@ -19489,9 +19112,8 @@
       <c r="K387" t="s">
         <v>13</v>
       </c>
-      <c r="O387" s="2"/>
-    </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="388" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
         <v>11</v>
       </c>
@@ -19525,9 +19147,8 @@
       <c r="K388" t="s">
         <v>13</v>
       </c>
-      <c r="O388" s="2"/>
-    </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="389" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
         <v>11</v>
       </c>
@@ -19561,9 +19182,8 @@
       <c r="K389" t="s">
         <v>13</v>
       </c>
-      <c r="O389" s="2"/>
-    </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="390" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
         <v>11</v>
       </c>
@@ -19597,9 +19217,8 @@
       <c r="K390" t="s">
         <v>13</v>
       </c>
-      <c r="O390" s="2"/>
-    </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="391" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
         <v>11</v>
       </c>
@@ -19633,9 +19252,8 @@
       <c r="K391" t="s">
         <v>13</v>
       </c>
-      <c r="O391" s="2"/>
-    </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="392" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
         <v>11</v>
       </c>
@@ -19669,9 +19287,8 @@
       <c r="K392" t="s">
         <v>13</v>
       </c>
-      <c r="O392" s="2"/>
-    </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="393" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
         <v>11</v>
       </c>
@@ -19705,9 +19322,8 @@
       <c r="K393" t="s">
         <v>13</v>
       </c>
-      <c r="O393" s="2"/>
-    </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="394" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
         <v>11</v>
       </c>
@@ -19741,9 +19357,8 @@
       <c r="K394" t="s">
         <v>13</v>
       </c>
-      <c r="O394" s="2"/>
-    </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="395" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
         <v>11</v>
       </c>
@@ -19777,9 +19392,8 @@
       <c r="K395" t="s">
         <v>13</v>
       </c>
-      <c r="O395" s="2"/>
-    </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="396" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
         <v>11</v>
       </c>
@@ -19813,9 +19427,8 @@
       <c r="K396" t="s">
         <v>13</v>
       </c>
-      <c r="O396" s="2"/>
-    </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="397" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
         <v>11</v>
       </c>
@@ -19849,9 +19462,8 @@
       <c r="K397" t="s">
         <v>13</v>
       </c>
-      <c r="O397" s="2"/>
-    </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="398" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
         <v>11</v>
       </c>
@@ -19885,9 +19497,8 @@
       <c r="K398" t="s">
         <v>13</v>
       </c>
-      <c r="O398" s="2"/>
-    </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="399" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
         <v>11</v>
       </c>
@@ -19921,9 +19532,8 @@
       <c r="K399" t="s">
         <v>13</v>
       </c>
-      <c r="O399" s="2"/>
-    </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="400" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
         <v>11</v>
       </c>
@@ -19957,9 +19567,8 @@
       <c r="K400" t="s">
         <v>13</v>
       </c>
-      <c r="O400" s="2"/>
-    </row>
-    <row r="401" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="401" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
         <v>11</v>
       </c>
@@ -19993,9 +19602,8 @@
       <c r="K401" t="s">
         <v>13</v>
       </c>
-      <c r="O401" s="2"/>
-    </row>
-    <row r="402" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="402" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
         <v>11</v>
       </c>
@@ -20029,9 +19637,8 @@
       <c r="K402" t="s">
         <v>13</v>
       </c>
-      <c r="O402" s="2"/>
-    </row>
-    <row r="403" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="403" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
         <v>11</v>
       </c>
@@ -20065,9 +19672,8 @@
       <c r="K403" t="s">
         <v>13</v>
       </c>
-      <c r="O403" s="2"/>
-    </row>
-    <row r="404" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="404" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
         <v>11</v>
       </c>
@@ -20101,9 +19707,8 @@
       <c r="K404" t="s">
         <v>13</v>
       </c>
-      <c r="O404" s="2"/>
-    </row>
-    <row r="405" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="405" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
         <v>11</v>
       </c>
@@ -20137,9 +19742,8 @@
       <c r="K405" t="s">
         <v>13</v>
       </c>
-      <c r="O405" s="2"/>
-    </row>
-    <row r="406" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="406" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
         <v>11</v>
       </c>
@@ -20173,9 +19777,8 @@
       <c r="K406" t="s">
         <v>13</v>
       </c>
-      <c r="O406" s="2"/>
-    </row>
-    <row r="407" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="407" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
         <v>11</v>
       </c>
@@ -20209,9 +19812,8 @@
       <c r="K407" t="s">
         <v>13</v>
       </c>
-      <c r="O407" s="2"/>
-    </row>
-    <row r="408" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="408" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
         <v>11</v>
       </c>
@@ -20245,9 +19847,8 @@
       <c r="K408" t="s">
         <v>13</v>
       </c>
-      <c r="O408" s="2"/>
-    </row>
-    <row r="409" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="409" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
         <v>11</v>
       </c>
@@ -20281,9 +19882,8 @@
       <c r="K409" t="s">
         <v>13</v>
       </c>
-      <c r="O409" s="2"/>
-    </row>
-    <row r="410" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="410" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
         <v>11</v>
       </c>
@@ -20317,9 +19917,8 @@
       <c r="K410" t="s">
         <v>13</v>
       </c>
-      <c r="O410" s="2"/>
-    </row>
-    <row r="411" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="411" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
         <v>11</v>
       </c>
@@ -20353,9 +19952,8 @@
       <c r="K411" t="s">
         <v>13</v>
       </c>
-      <c r="O411" s="2"/>
-    </row>
-    <row r="412" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="412" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
         <v>11</v>
       </c>
@@ -20389,9 +19987,8 @@
       <c r="K412" t="s">
         <v>13</v>
       </c>
-      <c r="O412" s="2"/>
-    </row>
-    <row r="413" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="413" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
         <v>11</v>
       </c>
@@ -20425,9 +20022,8 @@
       <c r="K413" t="s">
         <v>13</v>
       </c>
-      <c r="O413" s="2"/>
-    </row>
-    <row r="414" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="414" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A414" t="s">
         <v>11</v>
       </c>
@@ -20461,9 +20057,8 @@
       <c r="K414" t="s">
         <v>13</v>
       </c>
-      <c r="O414" s="2"/>
-    </row>
-    <row r="415" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="415" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A415" t="s">
         <v>11</v>
       </c>
@@ -20497,9 +20092,8 @@
       <c r="K415" t="s">
         <v>13</v>
       </c>
-      <c r="O415" s="2"/>
-    </row>
-    <row r="416" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="416" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A416" t="s">
         <v>11</v>
       </c>
@@ -20533,9 +20127,8 @@
       <c r="K416" t="s">
         <v>13</v>
       </c>
-      <c r="O416" s="2"/>
-    </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="417" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A417" t="s">
         <v>11</v>
       </c>
@@ -20569,9 +20162,8 @@
       <c r="K417" t="s">
         <v>13</v>
       </c>
-      <c r="O417" s="2"/>
-    </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="418" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A418" t="s">
         <v>11</v>
       </c>
@@ -20605,9 +20197,8 @@
       <c r="K418" t="s">
         <v>13</v>
       </c>
-      <c r="O418" s="2"/>
-    </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="419" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A419" t="s">
         <v>11</v>
       </c>
@@ -20641,9 +20232,8 @@
       <c r="K419" t="s">
         <v>13</v>
       </c>
-      <c r="O419" s="2"/>
-    </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="420" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A420" t="s">
         <v>11</v>
       </c>
@@ -20677,9 +20267,8 @@
       <c r="K420" t="s">
         <v>13</v>
       </c>
-      <c r="O420" s="2"/>
-    </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="421" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A421" t="s">
         <v>11</v>
       </c>
@@ -20713,9 +20302,8 @@
       <c r="K421" t="s">
         <v>13</v>
       </c>
-      <c r="O421" s="2"/>
-    </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="422" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A422" t="s">
         <v>11</v>
       </c>
@@ -20749,9 +20337,8 @@
       <c r="K422" t="s">
         <v>13</v>
       </c>
-      <c r="O422" s="2"/>
-    </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="423" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A423" t="s">
         <v>11</v>
       </c>
@@ -20785,9 +20372,8 @@
       <c r="K423" t="s">
         <v>13</v>
       </c>
-      <c r="O423" s="2"/>
-    </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="424" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A424" t="s">
         <v>11</v>
       </c>
@@ -20821,9 +20407,8 @@
       <c r="K424" t="s">
         <v>13</v>
       </c>
-      <c r="O424" s="2"/>
-    </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="425" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A425" t="s">
         <v>11</v>
       </c>
@@ -20857,9 +20442,8 @@
       <c r="K425" t="s">
         <v>13</v>
       </c>
-      <c r="O425" s="2"/>
-    </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="426" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A426" t="s">
         <v>11</v>
       </c>
@@ -20893,9 +20477,8 @@
       <c r="K426" t="s">
         <v>13</v>
       </c>
-      <c r="O426" s="2"/>
-    </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="427" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A427" t="s">
         <v>11</v>
       </c>
@@ -20929,9 +20512,8 @@
       <c r="K427" t="s">
         <v>13</v>
       </c>
-      <c r="O427" s="2"/>
-    </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="428" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A428" t="s">
         <v>11</v>
       </c>
@@ -20965,9 +20547,8 @@
       <c r="K428" t="s">
         <v>13</v>
       </c>
-      <c r="O428" s="2"/>
-    </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="429" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A429" t="s">
         <v>11</v>
       </c>
@@ -21001,9 +20582,8 @@
       <c r="K429" t="s">
         <v>13</v>
       </c>
-      <c r="O429" s="2"/>
-    </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="430" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A430" t="s">
         <v>11</v>
       </c>
@@ -21037,9 +20617,8 @@
       <c r="K430" t="s">
         <v>13</v>
       </c>
-      <c r="O430" s="2"/>
-    </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="431" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A431" t="s">
         <v>11</v>
       </c>
@@ -21073,9 +20652,8 @@
       <c r="K431" t="s">
         <v>13</v>
       </c>
-      <c r="O431" s="2"/>
-    </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="432" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A432" t="s">
         <v>11</v>
       </c>
@@ -21109,9 +20687,8 @@
       <c r="K432" t="s">
         <v>13</v>
       </c>
-      <c r="O432" s="2"/>
-    </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="433" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
         <v>11</v>
       </c>
@@ -21145,9 +20722,8 @@
       <c r="K433" t="s">
         <v>13</v>
       </c>
-      <c r="O433" s="2"/>
-    </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="434" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
         <v>11</v>
       </c>
@@ -21181,9 +20757,8 @@
       <c r="K434" t="s">
         <v>13</v>
       </c>
-      <c r="O434" s="2"/>
-    </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="435" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
         <v>11</v>
       </c>
@@ -21217,9 +20792,8 @@
       <c r="K435" t="s">
         <v>13</v>
       </c>
-      <c r="O435" s="2"/>
-    </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="436" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
         <v>11</v>
       </c>
@@ -21253,9 +20827,8 @@
       <c r="K436" t="s">
         <v>13</v>
       </c>
-      <c r="O436" s="2"/>
-    </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="437" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
         <v>11</v>
       </c>
@@ -21289,9 +20862,8 @@
       <c r="K437" t="s">
         <v>13</v>
       </c>
-      <c r="O437" s="2"/>
-    </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="438" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
         <v>11</v>
       </c>
@@ -21325,9 +20897,8 @@
       <c r="K438" t="s">
         <v>13</v>
       </c>
-      <c r="O438" s="2"/>
-    </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="439" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
         <v>11</v>
       </c>
@@ -21361,9 +20932,8 @@
       <c r="K439" t="s">
         <v>13</v>
       </c>
-      <c r="O439" s="2"/>
-    </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="440" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
         <v>11</v>
       </c>
@@ -21397,9 +20967,8 @@
       <c r="K440" t="s">
         <v>13</v>
       </c>
-      <c r="O440" s="2"/>
-    </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="441" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A441" t="s">
         <v>11</v>
       </c>
@@ -21433,9 +21002,8 @@
       <c r="K441" t="s">
         <v>13</v>
       </c>
-      <c r="O441" s="2"/>
-    </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="442" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A442" t="s">
         <v>11</v>
       </c>
@@ -21469,9 +21037,8 @@
       <c r="K442" t="s">
         <v>13</v>
       </c>
-      <c r="O442" s="2"/>
-    </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="443" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A443" t="s">
         <v>11</v>
       </c>
@@ -21505,9 +21072,8 @@
       <c r="K443" t="s">
         <v>13</v>
       </c>
-      <c r="O443" s="2"/>
-    </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="444" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A444" t="s">
         <v>11</v>
       </c>
@@ -21541,9 +21107,8 @@
       <c r="K444" t="s">
         <v>13</v>
       </c>
-      <c r="O444" s="2"/>
-    </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="445" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A445" t="s">
         <v>11</v>
       </c>
@@ -21577,9 +21142,8 @@
       <c r="K445" t="s">
         <v>13</v>
       </c>
-      <c r="O445" s="2"/>
-    </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="446" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A446" t="s">
         <v>11</v>
       </c>
@@ -21613,9 +21177,8 @@
       <c r="K446" t="s">
         <v>13</v>
       </c>
-      <c r="O446" s="2"/>
-    </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="447" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A447" t="s">
         <v>11</v>
       </c>
@@ -21649,9 +21212,8 @@
       <c r="K447" t="s">
         <v>13</v>
       </c>
-      <c r="O447" s="2"/>
-    </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="448" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A448" t="s">
         <v>11</v>
       </c>
@@ -21685,9 +21247,8 @@
       <c r="K448" t="s">
         <v>13</v>
       </c>
-      <c r="O448" s="2"/>
-    </row>
-    <row r="449" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="449" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A449" t="s">
         <v>11</v>
       </c>
@@ -21721,9 +21282,8 @@
       <c r="K449" t="s">
         <v>13</v>
       </c>
-      <c r="O449" s="2"/>
-    </row>
-    <row r="450" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="450" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A450" t="s">
         <v>11</v>
       </c>
@@ -21757,9 +21317,8 @@
       <c r="K450" t="s">
         <v>13</v>
       </c>
-      <c r="O450" s="2"/>
-    </row>
-    <row r="451" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="451" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A451" t="s">
         <v>11</v>
       </c>
@@ -21793,9 +21352,8 @@
       <c r="K451" t="s">
         <v>13</v>
       </c>
-      <c r="O451" s="2"/>
-    </row>
-    <row r="452" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="452" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A452" t="s">
         <v>11</v>
       </c>
@@ -21829,9 +21387,8 @@
       <c r="K452" t="s">
         <v>13</v>
       </c>
-      <c r="O452" s="2"/>
-    </row>
-    <row r="453" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="453" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A453" t="s">
         <v>11</v>
       </c>
@@ -21865,9 +21422,8 @@
       <c r="K453" t="s">
         <v>13</v>
       </c>
-      <c r="O453" s="2"/>
-    </row>
-    <row r="454" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="454" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A454" t="s">
         <v>11</v>
       </c>
@@ -21901,9 +21457,8 @@
       <c r="K454" t="s">
         <v>13</v>
       </c>
-      <c r="O454" s="2"/>
-    </row>
-    <row r="455" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="455" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A455" t="s">
         <v>11</v>
       </c>
@@ -21937,9 +21492,8 @@
       <c r="K455" t="s">
         <v>13</v>
       </c>
-      <c r="O455" s="2"/>
-    </row>
-    <row r="456" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="456" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A456" t="s">
         <v>11</v>
       </c>
@@ -21973,9 +21527,8 @@
       <c r="K456" t="s">
         <v>13</v>
       </c>
-      <c r="O456" s="2"/>
-    </row>
-    <row r="457" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="457" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A457" t="s">
         <v>11</v>
       </c>
@@ -22009,9 +21562,8 @@
       <c r="K457" t="s">
         <v>13</v>
       </c>
-      <c r="O457" s="2"/>
-    </row>
-    <row r="458" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="458" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A458" t="s">
         <v>11</v>
       </c>
@@ -22045,9 +21597,8 @@
       <c r="K458" t="s">
         <v>13</v>
       </c>
-      <c r="O458" s="2"/>
-    </row>
-    <row r="459" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="459" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A459" t="s">
         <v>11</v>
       </c>
@@ -22081,9 +21632,8 @@
       <c r="K459" t="s">
         <v>13</v>
       </c>
-      <c r="O459" s="2"/>
-    </row>
-    <row r="460" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="460" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A460" t="s">
         <v>11</v>
       </c>
@@ -22117,9 +21667,8 @@
       <c r="K460" t="s">
         <v>13</v>
       </c>
-      <c r="O460" s="2"/>
-    </row>
-    <row r="461" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="461" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A461" t="s">
         <v>11</v>
       </c>
@@ -22153,9 +21702,8 @@
       <c r="K461" t="s">
         <v>13</v>
       </c>
-      <c r="O461" s="2"/>
-    </row>
-    <row r="462" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="462" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A462" t="s">
         <v>11</v>
       </c>
@@ -22189,9 +21737,8 @@
       <c r="K462" t="s">
         <v>13</v>
       </c>
-      <c r="O462" s="2"/>
-    </row>
-    <row r="463" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="463" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A463" t="s">
         <v>11</v>
       </c>
@@ -22225,9 +21772,8 @@
       <c r="K463" t="s">
         <v>13</v>
       </c>
-      <c r="O463" s="2"/>
-    </row>
-    <row r="464" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="464" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A464" t="s">
         <v>11</v>
       </c>
@@ -22261,9 +21807,8 @@
       <c r="K464" t="s">
         <v>621</v>
       </c>
-      <c r="O464" s="2"/>
-    </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="465" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A465" t="s">
         <v>11</v>
       </c>
@@ -22297,9 +21842,8 @@
       <c r="K465" t="s">
         <v>13</v>
       </c>
-      <c r="O465" s="2"/>
-    </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="466" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A466" t="s">
         <v>11</v>
       </c>
@@ -22333,9 +21877,8 @@
       <c r="K466" t="s">
         <v>13</v>
       </c>
-      <c r="O466" s="2"/>
-    </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="467" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A467" t="s">
         <v>11</v>
       </c>
@@ -22369,9 +21912,8 @@
       <c r="K467" t="s">
         <v>13</v>
       </c>
-      <c r="O467" s="2"/>
-    </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="468" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A468" t="s">
         <v>11</v>
       </c>
@@ -22405,9 +21947,8 @@
       <c r="K468" t="s">
         <v>13</v>
       </c>
-      <c r="O468" s="2"/>
-    </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="469" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A469" t="s">
         <v>11</v>
       </c>
@@ -22441,9 +21982,8 @@
       <c r="K469" t="s">
         <v>13</v>
       </c>
-      <c r="O469" s="2"/>
-    </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="470" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A470" t="s">
         <v>11</v>
       </c>
@@ -22477,9 +22017,8 @@
       <c r="K470" t="s">
         <v>13</v>
       </c>
-      <c r="O470" s="2"/>
-    </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="471" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A471" t="s">
         <v>11</v>
       </c>
@@ -22513,9 +22052,8 @@
       <c r="K471" t="s">
         <v>13</v>
       </c>
-      <c r="O471" s="2"/>
-    </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="472" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A472" t="s">
         <v>11</v>
       </c>
@@ -22549,9 +22087,8 @@
       <c r="K472" t="s">
         <v>13</v>
       </c>
-      <c r="O472" s="2"/>
-    </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="473" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A473" t="s">
         <v>11</v>
       </c>
@@ -22585,9 +22122,8 @@
       <c r="K473" t="s">
         <v>13</v>
       </c>
-      <c r="O473" s="2"/>
-    </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="474" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A474" t="s">
         <v>11</v>
       </c>
@@ -22621,9 +22157,8 @@
       <c r="K474" t="s">
         <v>13</v>
       </c>
-      <c r="O474" s="2"/>
-    </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="475" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A475" t="s">
         <v>11</v>
       </c>
@@ -22657,9 +22192,8 @@
       <c r="K475" t="s">
         <v>13</v>
       </c>
-      <c r="O475" s="2"/>
-    </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="476" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
         <v>11</v>
       </c>
@@ -22693,9 +22227,8 @@
       <c r="K476" t="s">
         <v>13</v>
       </c>
-      <c r="O476" s="2"/>
-    </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="477" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
         <v>11</v>
       </c>
@@ -22729,9 +22262,8 @@
       <c r="K477" t="s">
         <v>13</v>
       </c>
-      <c r="O477" s="2"/>
-    </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="478" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
         <v>11</v>
       </c>
@@ -22765,9 +22297,8 @@
       <c r="K478" t="s">
         <v>13</v>
       </c>
-      <c r="O478" s="2"/>
-    </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="479" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
         <v>11</v>
       </c>
@@ -22801,9 +22332,8 @@
       <c r="K479" t="s">
         <v>13</v>
       </c>
-      <c r="O479" s="2"/>
-    </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="480" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
         <v>11</v>
       </c>
@@ -22837,9 +22367,8 @@
       <c r="K480" t="s">
         <v>13</v>
       </c>
-      <c r="O480" s="2"/>
-    </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="481" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
         <v>11</v>
       </c>
@@ -22873,9 +22402,8 @@
       <c r="K481" t="s">
         <v>13</v>
       </c>
-      <c r="O481" s="2"/>
-    </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="482" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
         <v>11</v>
       </c>
@@ -22909,9 +22437,8 @@
       <c r="K482" t="s">
         <v>13</v>
       </c>
-      <c r="O482" s="2"/>
-    </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="483" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
         <v>11</v>
       </c>
@@ -22945,9 +22472,8 @@
       <c r="K483" t="s">
         <v>13</v>
       </c>
-      <c r="O483" s="2"/>
-    </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="484" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A484" t="s">
         <v>11</v>
       </c>
@@ -22981,9 +22507,8 @@
       <c r="K484" t="s">
         <v>13</v>
       </c>
-      <c r="O484" s="2"/>
-    </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="485" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A485" t="s">
         <v>11</v>
       </c>
@@ -23017,9 +22542,8 @@
       <c r="K485" t="s">
         <v>13</v>
       </c>
-      <c r="O485" s="2"/>
-    </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="486" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A486" t="s">
         <v>11</v>
       </c>
@@ -23053,9 +22577,8 @@
       <c r="K486" t="s">
         <v>13</v>
       </c>
-      <c r="O486" s="2"/>
-    </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="487" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A487" t="s">
         <v>11</v>
       </c>
@@ -23089,9 +22612,8 @@
       <c r="K487" t="s">
         <v>13</v>
       </c>
-      <c r="O487" s="2"/>
-    </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="488" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A488" t="s">
         <v>11</v>
       </c>
@@ -23125,9 +22647,8 @@
       <c r="K488" t="s">
         <v>13</v>
       </c>
-      <c r="O488" s="2"/>
-    </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="489" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A489" t="s">
         <v>11</v>
       </c>
@@ -23161,9 +22682,8 @@
       <c r="K489" t="s">
         <v>13</v>
       </c>
-      <c r="O489" s="2"/>
-    </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="490" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A490" t="s">
         <v>11</v>
       </c>
@@ -23197,9 +22717,8 @@
       <c r="K490" t="s">
         <v>13</v>
       </c>
-      <c r="O490" s="2"/>
-    </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="491" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A491" t="s">
         <v>11</v>
       </c>
@@ -23233,9 +22752,8 @@
       <c r="K491" t="s">
         <v>13</v>
       </c>
-      <c r="O491" s="2"/>
-    </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="492" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A492" t="s">
         <v>11</v>
       </c>
@@ -23269,9 +22787,8 @@
       <c r="K492" t="s">
         <v>13</v>
       </c>
-      <c r="O492" s="2"/>
-    </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="493" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A493" t="s">
         <v>11</v>
       </c>
@@ -23305,9 +22822,8 @@
       <c r="K493" t="s">
         <v>13</v>
       </c>
-      <c r="O493" s="2"/>
-    </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="494" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A494" t="s">
         <v>11</v>
       </c>
@@ -23341,9 +22857,8 @@
       <c r="K494" t="s">
         <v>13</v>
       </c>
-      <c r="O494" s="2"/>
-    </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="495" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A495" t="s">
         <v>11</v>
       </c>
@@ -23377,9 +22892,8 @@
       <c r="K495" t="s">
         <v>13</v>
       </c>
-      <c r="O495" s="2"/>
-    </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="496" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A496" t="s">
         <v>11</v>
       </c>
@@ -23413,7 +22927,6 @@
       <c r="K496" t="s">
         <v>13</v>
       </c>
-      <c r="O496" s="2"/>
     </row>
     <row r="497" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A497" t="s">
@@ -23449,7 +22962,6 @@
       <c r="K497" t="s">
         <v>13</v>
       </c>
-      <c r="O497" s="2"/>
     </row>
     <row r="498" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A498" t="s">
@@ -23485,7 +22997,6 @@
       <c r="K498" t="s">
         <v>13</v>
       </c>
-      <c r="O498" s="2"/>
     </row>
     <row r="499" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A499" t="s">
@@ -23521,7 +23032,6 @@
       <c r="K499" t="s">
         <v>13</v>
       </c>
-      <c r="O499" s="2"/>
     </row>
     <row r="500" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A500" t="s">
@@ -23557,7 +23067,6 @@
       <c r="K500" t="s">
         <v>13</v>
       </c>
-      <c r="O500" s="2"/>
     </row>
     <row r="501" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A501" t="s">
@@ -23593,7 +23102,6 @@
       <c r="K501" t="s">
         <v>13</v>
       </c>
-      <c r="O501" s="2"/>
     </row>
     <row r="502" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A502" t="s">
@@ -23667,7 +23175,6 @@
       <c r="K503" t="s">
         <v>13</v>
       </c>
-      <c r="O503" s="2"/>
     </row>
     <row r="504" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A504" t="s">
@@ -23703,7 +23210,6 @@
       <c r="K504" t="s">
         <v>13</v>
       </c>
-      <c r="O504" s="2"/>
     </row>
     <row r="505" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A505" t="s">
@@ -23739,7 +23245,6 @@
       <c r="K505" t="s">
         <v>13</v>
       </c>
-      <c r="O505" s="2"/>
     </row>
     <row r="506" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A506" t="s">
@@ -23775,7 +23280,6 @@
       <c r="K506" t="s">
         <v>13</v>
       </c>
-      <c r="O506" s="2"/>
     </row>
     <row r="507" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A507" t="s">
@@ -23811,7 +23315,6 @@
       <c r="K507" t="s">
         <v>13</v>
       </c>
-      <c r="O507" s="2"/>
     </row>
     <row r="508" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A508" t="s">
@@ -23847,7 +23350,6 @@
       <c r="K508" t="s">
         <v>13</v>
       </c>
-      <c r="O508" s="2"/>
     </row>
     <row r="509" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A509" t="s">
@@ -23883,7 +23385,6 @@
       <c r="K509" t="s">
         <v>13</v>
       </c>
-      <c r="O509" s="2"/>
     </row>
     <row r="510" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A510" t="s">
@@ -23919,7 +23420,6 @@
       <c r="K510" t="s">
         <v>13</v>
       </c>
-      <c r="O510" s="2"/>
     </row>
     <row r="511" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A511" t="s">
@@ -23955,7 +23455,6 @@
       <c r="K511" t="s">
         <v>13</v>
       </c>
-      <c r="O511" s="2"/>
     </row>
     <row r="512" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A512" t="s">
@@ -23991,9 +23490,8 @@
       <c r="K512" t="s">
         <v>13</v>
       </c>
-      <c r="O512" s="2"/>
-    </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="513" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A513" t="s">
         <v>11</v>
       </c>
@@ -24027,9 +23525,8 @@
       <c r="K513" t="s">
         <v>13</v>
       </c>
-      <c r="O513" s="2"/>
-    </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="514" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A514" t="s">
         <v>11</v>
       </c>
@@ -24063,9 +23560,8 @@
       <c r="K514" t="s">
         <v>13</v>
       </c>
-      <c r="O514" s="2"/>
-    </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="515" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A515" t="s">
         <v>11</v>
       </c>
@@ -24099,9 +23595,8 @@
       <c r="K515" t="s">
         <v>13</v>
       </c>
-      <c r="O515" s="2"/>
-    </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="516" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A516" t="s">
         <v>11</v>
       </c>
@@ -24135,9 +23630,8 @@
       <c r="K516" t="s">
         <v>13</v>
       </c>
-      <c r="O516" s="2"/>
-    </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="517" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A517" t="s">
         <v>11</v>
       </c>
@@ -24171,9 +23665,8 @@
       <c r="K517" t="s">
         <v>13</v>
       </c>
-      <c r="O517" s="2"/>
-    </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="518" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A518" t="s">
         <v>11</v>
       </c>
@@ -24207,9 +23700,8 @@
       <c r="K518" t="s">
         <v>13</v>
       </c>
-      <c r="O518" s="2"/>
-    </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="519" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A519" t="s">
         <v>11</v>
       </c>
@@ -24243,9 +23735,8 @@
       <c r="K519" t="s">
         <v>13</v>
       </c>
-      <c r="O519" s="2"/>
-    </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="520" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A520" t="s">
         <v>11</v>
       </c>
@@ -24279,9 +23770,8 @@
       <c r="K520" t="s">
         <v>13</v>
       </c>
-      <c r="O520" s="2"/>
-    </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="521" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A521" t="s">
         <v>11</v>
       </c>
@@ -24315,9 +23805,8 @@
       <c r="K521" t="s">
         <v>13</v>
       </c>
-      <c r="O521" s="2"/>
-    </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="522" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A522" t="s">
         <v>11</v>
       </c>
@@ -24351,9 +23840,8 @@
       <c r="K522" t="s">
         <v>13</v>
       </c>
-      <c r="O522" s="2"/>
-    </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="523" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A523" t="s">
         <v>11</v>
       </c>
@@ -24387,9 +23875,8 @@
       <c r="K523" t="s">
         <v>13</v>
       </c>
-      <c r="O523" s="2"/>
-    </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="524" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A524" t="s">
         <v>11</v>
       </c>
@@ -24423,9 +23910,8 @@
       <c r="K524" t="s">
         <v>13</v>
       </c>
-      <c r="O524" s="2"/>
-    </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="525" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A525" t="s">
         <v>11</v>
       </c>
@@ -24459,9 +23945,8 @@
       <c r="K525" t="s">
         <v>13</v>
       </c>
-      <c r="O525" s="2"/>
-    </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="526" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A526" t="s">
         <v>11</v>
       </c>
@@ -24495,9 +23980,8 @@
       <c r="K526" t="s">
         <v>13</v>
       </c>
-      <c r="O526" s="2"/>
-    </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="527" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A527" t="s">
         <v>11</v>
       </c>
@@ -24531,9 +24015,8 @@
       <c r="K527" t="s">
         <v>13</v>
       </c>
-      <c r="O527" s="2"/>
-    </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="528" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A528" t="s">
         <v>11</v>
       </c>
@@ -24567,7 +24050,6 @@
       <c r="K528" t="s">
         <v>13</v>
       </c>
-      <c r="O528" s="2"/>
     </row>
     <row r="529" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A529" t="s">
@@ -24603,7 +24085,6 @@
       <c r="K529" t="s">
         <v>13</v>
       </c>
-      <c r="O529" s="2"/>
     </row>
     <row r="530" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A530" t="s">
@@ -24639,7 +24120,6 @@
       <c r="K530" t="s">
         <v>13</v>
       </c>
-      <c r="O530" s="2"/>
     </row>
     <row r="531" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A531" t="s">
@@ -24675,7 +24155,6 @@
       <c r="K531" t="s">
         <v>13</v>
       </c>
-      <c r="O531" s="2"/>
     </row>
     <row r="532" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A532" t="s">
@@ -24711,7 +24190,6 @@
       <c r="K532" t="s">
         <v>13</v>
       </c>
-      <c r="O532" s="2"/>
     </row>
     <row r="533" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A533" t="s">
@@ -24747,7 +24225,6 @@
       <c r="K533" t="s">
         <v>13</v>
       </c>
-      <c r="O533" s="2"/>
     </row>
     <row r="534" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A534" t="s">
@@ -24783,7 +24260,6 @@
       <c r="K534" t="s">
         <v>13</v>
       </c>
-      <c r="O534" s="2"/>
     </row>
     <row r="535" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A535" t="s">
@@ -24819,7 +24295,6 @@
       <c r="K535" t="s">
         <v>13</v>
       </c>
-      <c r="O535" s="2"/>
     </row>
     <row r="536" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A536" t="s">
@@ -24855,7 +24330,7 @@
       <c r="K536" t="s">
         <v>13</v>
       </c>
-      <c r="O536" s="2" t="s">
+      <c r="O536" t="s">
         <v>1664</v>
       </c>
     </row>
@@ -24893,7 +24368,6 @@
       <c r="K537" t="s">
         <v>13</v>
       </c>
-      <c r="O537" s="2"/>
     </row>
     <row r="538" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A538" t="s">
@@ -24929,7 +24403,6 @@
       <c r="K538" t="s">
         <v>13</v>
       </c>
-      <c r="O538" s="2"/>
     </row>
     <row r="539" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A539" t="s">
@@ -24965,7 +24438,6 @@
       <c r="K539" t="s">
         <v>13</v>
       </c>
-      <c r="O539" s="2"/>
     </row>
     <row r="540" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A540" t="s">
@@ -25001,7 +24473,6 @@
       <c r="K540" t="s">
         <v>13</v>
       </c>
-      <c r="O540" s="2"/>
     </row>
     <row r="541" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A541" t="s">
@@ -25037,7 +24508,6 @@
       <c r="K541" t="s">
         <v>13</v>
       </c>
-      <c r="O541" s="2"/>
     </row>
     <row r="542" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A542" t="s">
@@ -25073,7 +24543,6 @@
       <c r="K542" t="s">
         <v>13</v>
       </c>
-      <c r="O542" s="2"/>
     </row>
     <row r="543" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A543" t="s">
@@ -25109,7 +24578,6 @@
       <c r="K543" t="s">
         <v>13</v>
       </c>
-      <c r="O543" s="2"/>
     </row>
     <row r="544" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A544" t="s">
@@ -25145,9 +24613,8 @@
       <c r="K544" t="s">
         <v>13</v>
       </c>
-      <c r="O544" s="2"/>
-    </row>
-    <row r="545" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="545" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A545" t="s">
         <v>11</v>
       </c>
@@ -25181,9 +24648,8 @@
       <c r="K545" t="s">
         <v>13</v>
       </c>
-      <c r="O545" s="2"/>
-    </row>
-    <row r="546" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="546" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A546" t="s">
         <v>11</v>
       </c>
@@ -25217,9 +24683,8 @@
       <c r="K546" t="s">
         <v>13</v>
       </c>
-      <c r="O546" s="2"/>
-    </row>
-    <row r="547" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="547" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A547" t="s">
         <v>98</v>
       </c>
@@ -25253,9 +24718,8 @@
       <c r="K547" t="s">
         <v>13</v>
       </c>
-      <c r="O547" s="2"/>
-    </row>
-    <row r="548" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="548" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A548" t="s">
         <v>11</v>
       </c>
@@ -25289,9 +24753,8 @@
       <c r="K548" t="s">
         <v>13</v>
       </c>
-      <c r="O548" s="2"/>
-    </row>
-    <row r="549" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="549" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A549" t="s">
         <v>11</v>
       </c>
@@ -25325,9 +24788,8 @@
       <c r="K549" t="s">
         <v>13</v>
       </c>
-      <c r="O549" s="2"/>
-    </row>
-    <row r="550" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="550" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A550" t="s">
         <v>11</v>
       </c>
@@ -25361,9 +24823,8 @@
       <c r="K550" t="s">
         <v>13</v>
       </c>
-      <c r="O550" s="2"/>
-    </row>
-    <row r="551" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="551" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A551" t="s">
         <v>11</v>
       </c>
@@ -25397,9 +24858,8 @@
       <c r="K551" t="s">
         <v>13</v>
       </c>
-      <c r="O551" s="2"/>
-    </row>
-    <row r="552" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="552" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A552" t="s">
         <v>11</v>
       </c>
@@ -25433,9 +24893,8 @@
       <c r="K552" t="s">
         <v>13</v>
       </c>
-      <c r="O552" s="2"/>
-    </row>
-    <row r="553" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="553" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A553" t="s">
         <v>11</v>
       </c>
@@ -25469,9 +24928,8 @@
       <c r="K553" t="s">
         <v>13</v>
       </c>
-      <c r="O553" s="2"/>
-    </row>
-    <row r="554" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="554" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A554" t="s">
         <v>11</v>
       </c>
@@ -25505,9 +24963,8 @@
       <c r="K554" t="s">
         <v>13</v>
       </c>
-      <c r="O554" s="2"/>
-    </row>
-    <row r="555" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="555" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A555" t="s">
         <v>11</v>
       </c>
@@ -25541,9 +24998,8 @@
       <c r="K555" t="s">
         <v>13</v>
       </c>
-      <c r="O555" s="2"/>
-    </row>
-    <row r="556" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="556" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A556" t="s">
         <v>11</v>
       </c>
@@ -25577,9 +25033,8 @@
       <c r="K556" t="s">
         <v>13</v>
       </c>
-      <c r="O556" s="2"/>
-    </row>
-    <row r="557" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="557" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A557" t="s">
         <v>11</v>
       </c>
@@ -25613,9 +25068,8 @@
       <c r="K557" t="s">
         <v>13</v>
       </c>
-      <c r="O557" s="2"/>
-    </row>
-    <row r="558" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="558" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A558" t="s">
         <v>11</v>
       </c>
@@ -25649,9 +25103,8 @@
       <c r="K558" t="s">
         <v>13</v>
       </c>
-      <c r="O558" s="2"/>
-    </row>
-    <row r="559" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="559" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A559" t="s">
         <v>11</v>
       </c>
@@ -25685,9 +25138,8 @@
       <c r="K559" t="s">
         <v>13</v>
       </c>
-      <c r="O559" s="2"/>
-    </row>
-    <row r="560" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="560" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A560" t="s">
         <v>11</v>
       </c>
@@ -25721,9 +25173,8 @@
       <c r="K560" t="s">
         <v>13</v>
       </c>
-      <c r="O560" s="2"/>
-    </row>
-    <row r="561" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="561" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A561" t="s">
         <v>11</v>
       </c>
@@ -25757,9 +25208,8 @@
       <c r="K561" t="s">
         <v>13</v>
       </c>
-      <c r="O561" s="2"/>
-    </row>
-    <row r="562" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="562" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A562" t="s">
         <v>11</v>
       </c>
@@ -25793,9 +25243,8 @@
       <c r="K562" t="s">
         <v>13</v>
       </c>
-      <c r="O562" s="2"/>
-    </row>
-    <row r="563" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="563" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A563" t="s">
         <v>98</v>
       </c>
@@ -25829,9 +25278,8 @@
       <c r="K563" t="s">
         <v>13</v>
       </c>
-      <c r="O563" s="2"/>
-    </row>
-    <row r="564" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="564" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A564" t="s">
         <v>98</v>
       </c>
@@ -25865,9 +25313,8 @@
       <c r="K564" t="s">
         <v>13</v>
       </c>
-      <c r="O564" s="2"/>
-    </row>
-    <row r="565" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="565" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A565" t="s">
         <v>11</v>
       </c>
@@ -25901,9 +25348,8 @@
       <c r="K565" t="s">
         <v>13</v>
       </c>
-      <c r="O565" s="2"/>
-    </row>
-    <row r="566" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="566" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A566" t="s">
         <v>11</v>
       </c>
@@ -25937,9 +25383,8 @@
       <c r="K566" t="s">
         <v>13</v>
       </c>
-      <c r="O566" s="2"/>
-    </row>
-    <row r="567" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="567" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A567" t="s">
         <v>11</v>
       </c>
@@ -25973,9 +25418,8 @@
       <c r="K567" t="s">
         <v>13</v>
       </c>
-      <c r="O567" s="2"/>
-    </row>
-    <row r="568" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="568" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A568" t="s">
         <v>11</v>
       </c>
@@ -26009,9 +25453,8 @@
       <c r="K568" t="s">
         <v>13</v>
       </c>
-      <c r="O568" s="2"/>
-    </row>
-    <row r="569" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="569" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A569" t="s">
         <v>11</v>
       </c>
@@ -26045,9 +25488,8 @@
       <c r="K569" t="s">
         <v>13</v>
       </c>
-      <c r="O569" s="2"/>
-    </row>
-    <row r="570" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="570" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A570" t="s">
         <v>11</v>
       </c>
@@ -26081,9 +25523,8 @@
       <c r="K570" t="s">
         <v>13</v>
       </c>
-      <c r="O570" s="2"/>
-    </row>
-    <row r="571" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="571" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A571" t="s">
         <v>11</v>
       </c>
@@ -26117,9 +25558,8 @@
       <c r="K571" t="s">
         <v>13</v>
       </c>
-      <c r="O571" s="2"/>
-    </row>
-    <row r="572" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="572" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A572" t="s">
         <v>11</v>
       </c>
@@ -26153,9 +25593,8 @@
       <c r="K572" t="s">
         <v>13</v>
       </c>
-      <c r="O572" s="2"/>
-    </row>
-    <row r="573" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="573" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A573" t="s">
         <v>11</v>
       </c>
@@ -26189,9 +25628,8 @@
       <c r="K573" t="s">
         <v>13</v>
       </c>
-      <c r="O573" s="2"/>
-    </row>
-    <row r="574" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="574" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A574" t="s">
         <v>11</v>
       </c>
@@ -26225,9 +25663,8 @@
       <c r="K574" t="s">
         <v>13</v>
       </c>
-      <c r="O574" s="2"/>
-    </row>
-    <row r="575" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="575" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A575" t="s">
         <v>11</v>
       </c>
@@ -26261,9 +25698,8 @@
       <c r="K575" t="s">
         <v>13</v>
       </c>
-      <c r="O575" s="2"/>
-    </row>
-    <row r="576" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="576" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A576" t="s">
         <v>11</v>
       </c>
@@ -26297,9 +25733,8 @@
       <c r="K576" t="s">
         <v>13</v>
       </c>
-      <c r="O576" s="2"/>
-    </row>
-    <row r="577" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="577" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A577" t="s">
         <v>11</v>
       </c>
@@ -26333,9 +25768,8 @@
       <c r="K577" t="s">
         <v>13</v>
       </c>
-      <c r="O577" s="2"/>
-    </row>
-    <row r="578" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="578" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A578" t="s">
         <v>11</v>
       </c>
@@ -26369,9 +25803,8 @@
       <c r="K578" t="s">
         <v>13</v>
       </c>
-      <c r="O578" s="2"/>
-    </row>
-    <row r="579" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="579" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A579" t="s">
         <v>11</v>
       </c>
@@ -26405,9 +25838,8 @@
       <c r="K579" t="s">
         <v>13</v>
       </c>
-      <c r="O579" s="2"/>
-    </row>
-    <row r="580" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="580" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A580" t="s">
         <v>11</v>
       </c>
@@ -26441,9 +25873,8 @@
       <c r="K580" t="s">
         <v>13</v>
       </c>
-      <c r="O580" s="2"/>
-    </row>
-    <row r="581" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="581" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A581" t="s">
         <v>11</v>
       </c>
@@ -26477,9 +25908,8 @@
       <c r="K581" t="s">
         <v>13</v>
       </c>
-      <c r="O581" s="2"/>
-    </row>
-    <row r="582" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="582" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A582" t="s">
         <v>11</v>
       </c>
@@ -26513,9 +25943,8 @@
       <c r="K582" t="s">
         <v>13</v>
       </c>
-      <c r="O582" s="2"/>
-    </row>
-    <row r="583" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="583" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A583" t="s">
         <v>11</v>
       </c>
@@ -26549,9 +25978,8 @@
       <c r="K583" t="s">
         <v>13</v>
       </c>
-      <c r="O583" s="2"/>
-    </row>
-    <row r="584" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="584" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A584" t="s">
         <v>11</v>
       </c>
@@ -26585,9 +26013,8 @@
       <c r="K584" t="s">
         <v>13</v>
       </c>
-      <c r="O584" s="2"/>
-    </row>
-    <row r="585" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="585" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A585" t="s">
         <v>11</v>
       </c>
@@ -26621,9 +26048,8 @@
       <c r="K585" t="s">
         <v>13</v>
       </c>
-      <c r="O585" s="2"/>
-    </row>
-    <row r="586" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="586" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A586" t="s">
         <v>11</v>
       </c>
@@ -26657,9 +26083,8 @@
       <c r="K586" t="s">
         <v>13</v>
       </c>
-      <c r="O586" s="2"/>
-    </row>
-    <row r="587" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="587" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A587" t="s">
         <v>11</v>
       </c>
@@ -26693,9 +26118,8 @@
       <c r="K587" t="s">
         <v>13</v>
       </c>
-      <c r="O587" s="2"/>
-    </row>
-    <row r="588" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="588" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A588" t="s">
         <v>11</v>
       </c>
@@ -26729,9 +26153,8 @@
       <c r="K588" t="s">
         <v>13</v>
       </c>
-      <c r="O588" s="2"/>
-    </row>
-    <row r="589" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="589" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A589" t="s">
         <v>11</v>
       </c>
@@ -26765,9 +26188,8 @@
       <c r="K589" t="s">
         <v>13</v>
       </c>
-      <c r="O589" s="2"/>
-    </row>
-    <row r="590" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="590" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A590" t="s">
         <v>11</v>
       </c>
@@ -26801,9 +26223,8 @@
       <c r="K590" t="s">
         <v>13</v>
       </c>
-      <c r="O590" s="2"/>
-    </row>
-    <row r="591" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="591" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A591" t="s">
         <v>11</v>
       </c>
@@ -26837,9 +26258,8 @@
       <c r="K591" t="s">
         <v>13</v>
       </c>
-      <c r="O591" s="2"/>
-    </row>
-    <row r="592" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="592" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A592" t="s">
         <v>11</v>
       </c>
@@ -26873,9 +26293,8 @@
       <c r="K592" t="s">
         <v>13</v>
       </c>
-      <c r="O592" s="2"/>
-    </row>
-    <row r="593" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="593" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A593" t="s">
         <v>11</v>
       </c>
@@ -26909,9 +26328,8 @@
       <c r="K593" t="s">
         <v>13</v>
       </c>
-      <c r="O593" s="2"/>
-    </row>
-    <row r="594" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="594" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A594" t="s">
         <v>11</v>
       </c>
@@ -26945,9 +26363,8 @@
       <c r="K594" t="s">
         <v>13</v>
       </c>
-      <c r="O594" s="2"/>
-    </row>
-    <row r="595" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="595" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A595" t="s">
         <v>11</v>
       </c>
@@ -26981,9 +26398,8 @@
       <c r="K595" t="s">
         <v>13</v>
       </c>
-      <c r="O595" s="2"/>
-    </row>
-    <row r="596" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="596" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A596" t="s">
         <v>11</v>
       </c>
@@ -27017,9 +26433,8 @@
       <c r="K596" t="s">
         <v>13</v>
       </c>
-      <c r="O596" s="2"/>
-    </row>
-    <row r="597" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="597" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A597" t="s">
         <v>11</v>
       </c>
@@ -27053,9 +26468,8 @@
       <c r="K597" t="s">
         <v>13</v>
       </c>
-      <c r="O597" s="2"/>
-    </row>
-    <row r="598" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="598" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A598" t="s">
         <v>98</v>
       </c>
@@ -27089,9 +26503,8 @@
       <c r="K598" t="s">
         <v>13</v>
       </c>
-      <c r="O598" s="2"/>
-    </row>
-    <row r="599" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="599" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A599" t="s">
         <v>11</v>
       </c>
@@ -27125,9 +26538,8 @@
       <c r="K599" t="s">
         <v>13</v>
       </c>
-      <c r="O599" s="2"/>
-    </row>
-    <row r="600" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="600" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A600" t="s">
         <v>98</v>
       </c>
@@ -27161,9 +26573,8 @@
       <c r="K600" t="s">
         <v>13</v>
       </c>
-      <c r="O600" s="2"/>
-    </row>
-    <row r="601" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="601" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A601" t="s">
         <v>11</v>
       </c>
@@ -27197,9 +26608,8 @@
       <c r="K601" t="s">
         <v>13</v>
       </c>
-      <c r="O601" s="2"/>
-    </row>
-    <row r="602" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="602" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A602" t="s">
         <v>11</v>
       </c>
@@ -27233,9 +26643,8 @@
       <c r="K602" t="s">
         <v>13</v>
       </c>
-      <c r="O602" s="2"/>
-    </row>
-    <row r="603" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="603" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A603" t="s">
         <v>11</v>
       </c>
@@ -27269,9 +26678,8 @@
       <c r="K603" t="s">
         <v>13</v>
       </c>
-      <c r="O603" s="2"/>
-    </row>
-    <row r="604" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="604" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A604" t="s">
         <v>11</v>
       </c>
@@ -27305,9 +26713,8 @@
       <c r="K604" t="s">
         <v>13</v>
       </c>
-      <c r="O604" s="2"/>
-    </row>
-    <row r="605" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="605" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A605" t="s">
         <v>11</v>
       </c>
@@ -27341,9 +26748,8 @@
       <c r="K605" t="s">
         <v>13</v>
       </c>
-      <c r="O605" s="2"/>
-    </row>
-    <row r="606" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="606" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A606" t="s">
         <v>11</v>
       </c>
@@ -27377,9 +26783,8 @@
       <c r="K606" t="s">
         <v>13</v>
       </c>
-      <c r="O606" s="2"/>
-    </row>
-    <row r="607" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="607" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A607" t="s">
         <v>11</v>
       </c>
@@ -27413,9 +26818,8 @@
       <c r="K607" t="s">
         <v>13</v>
       </c>
-      <c r="O607" s="2"/>
-    </row>
-    <row r="608" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="608" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A608" t="s">
         <v>11</v>
       </c>
@@ -27449,9 +26853,8 @@
       <c r="K608" t="s">
         <v>13</v>
       </c>
-      <c r="O608" s="2"/>
-    </row>
-    <row r="609" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="609" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A609" t="s">
         <v>11</v>
       </c>
@@ -27485,9 +26888,8 @@
       <c r="K609" t="s">
         <v>13</v>
       </c>
-      <c r="O609" s="2"/>
-    </row>
-    <row r="610" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="610" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A610" t="s">
         <v>11</v>
       </c>
@@ -27521,9 +26923,8 @@
       <c r="K610" t="s">
         <v>13</v>
       </c>
-      <c r="O610" s="2"/>
-    </row>
-    <row r="611" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="611" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A611" t="s">
         <v>11</v>
       </c>
@@ -27557,9 +26958,8 @@
       <c r="K611" t="s">
         <v>13</v>
       </c>
-      <c r="O611" s="2"/>
-    </row>
-    <row r="612" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="612" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A612" t="s">
         <v>11</v>
       </c>
@@ -27593,9 +26993,8 @@
       <c r="K612" t="s">
         <v>13</v>
       </c>
-      <c r="O612" s="2"/>
-    </row>
-    <row r="613" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="613" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A613" t="s">
         <v>11</v>
       </c>
@@ -27629,9 +27028,8 @@
       <c r="K613" t="s">
         <v>13</v>
       </c>
-      <c r="O613" s="2"/>
-    </row>
-    <row r="614" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="614" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A614" t="s">
         <v>11</v>
       </c>
@@ -27665,9 +27063,8 @@
       <c r="K614" t="s">
         <v>13</v>
       </c>
-      <c r="O614" s="2"/>
-    </row>
-    <row r="615" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="615" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A615" t="s">
         <v>11</v>
       </c>
@@ -27701,9 +27098,8 @@
       <c r="K615" t="s">
         <v>13</v>
       </c>
-      <c r="O615" s="2"/>
-    </row>
-    <row r="616" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="616" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A616" t="s">
         <v>11</v>
       </c>
@@ -27737,9 +27133,8 @@
       <c r="K616" t="s">
         <v>13</v>
       </c>
-      <c r="O616" s="2"/>
-    </row>
-    <row r="617" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="617" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A617" t="s">
         <v>11</v>
       </c>
@@ -27773,9 +27168,8 @@
       <c r="K617" t="s">
         <v>13</v>
       </c>
-      <c r="O617" s="2"/>
-    </row>
-    <row r="618" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="618" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A618" t="s">
         <v>11</v>
       </c>
@@ -27809,9 +27203,8 @@
       <c r="K618" t="s">
         <v>13</v>
       </c>
-      <c r="O618" s="2"/>
-    </row>
-    <row r="619" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="619" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A619" t="s">
         <v>11</v>
       </c>
@@ -27845,9 +27238,8 @@
       <c r="K619" t="s">
         <v>13</v>
       </c>
-      <c r="O619" s="2"/>
-    </row>
-    <row r="620" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="620" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A620" t="s">
         <v>11</v>
       </c>
@@ -27881,9 +27273,8 @@
       <c r="K620" t="s">
         <v>13</v>
       </c>
-      <c r="O620" s="2"/>
-    </row>
-    <row r="621" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="621" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A621" t="s">
         <v>11</v>
       </c>
@@ -27917,9 +27308,8 @@
       <c r="K621" t="s">
         <v>13</v>
       </c>
-      <c r="O621" s="2"/>
-    </row>
-    <row r="622" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="622" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A622" t="s">
         <v>11</v>
       </c>
@@ -27953,9 +27343,8 @@
       <c r="K622" t="s">
         <v>13</v>
       </c>
-      <c r="O622" s="2"/>
-    </row>
-    <row r="623" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="623" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A623" t="s">
         <v>11</v>
       </c>
@@ -27989,9 +27378,8 @@
       <c r="K623" t="s">
         <v>13</v>
       </c>
-      <c r="O623" s="2"/>
-    </row>
-    <row r="624" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="624" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A624" t="s">
         <v>11</v>
       </c>
@@ -28025,9 +27413,8 @@
       <c r="K624" t="s">
         <v>13</v>
       </c>
-      <c r="O624" s="2"/>
-    </row>
-    <row r="625" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="625" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A625" t="s">
         <v>11</v>
       </c>
@@ -28061,9 +27448,8 @@
       <c r="K625" t="s">
         <v>13</v>
       </c>
-      <c r="O625" s="2"/>
-    </row>
-    <row r="626" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="626" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A626" t="s">
         <v>11</v>
       </c>
@@ -28097,9 +27483,8 @@
       <c r="K626" t="s">
         <v>13</v>
       </c>
-      <c r="O626" s="2"/>
-    </row>
-    <row r="627" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="627" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A627" t="s">
         <v>11</v>
       </c>
@@ -28133,9 +27518,8 @@
       <c r="K627" t="s">
         <v>13</v>
       </c>
-      <c r="O627" s="2"/>
-    </row>
-    <row r="628" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="628" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A628" t="s">
         <v>11</v>
       </c>
@@ -28169,9 +27553,8 @@
       <c r="K628" t="s">
         <v>13</v>
       </c>
-      <c r="O628" s="2"/>
-    </row>
-    <row r="629" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="629" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A629" t="s">
         <v>11</v>
       </c>
@@ -28205,9 +27588,8 @@
       <c r="K629" t="s">
         <v>13</v>
       </c>
-      <c r="O629" s="2"/>
-    </row>
-    <row r="630" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="630" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A630" t="s">
         <v>11</v>
       </c>
@@ -28241,9 +27623,8 @@
       <c r="K630" t="s">
         <v>13</v>
       </c>
-      <c r="O630" s="2"/>
-    </row>
-    <row r="631" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="631" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A631" t="s">
         <v>11</v>
       </c>
@@ -28277,9 +27658,8 @@
       <c r="K631" t="s">
         <v>13</v>
       </c>
-      <c r="O631" s="2"/>
-    </row>
-    <row r="632" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="632" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A632" t="s">
         <v>11</v>
       </c>
@@ -28313,9 +27693,8 @@
       <c r="K632" t="s">
         <v>13</v>
       </c>
-      <c r="O632" s="2"/>
-    </row>
-    <row r="633" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="633" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A633" t="s">
         <v>11</v>
       </c>
@@ -28349,9 +27728,8 @@
       <c r="K633" t="s">
         <v>13</v>
       </c>
-      <c r="O633" s="2"/>
-    </row>
-    <row r="634" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="634" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A634" t="s">
         <v>11</v>
       </c>
@@ -28385,9 +27763,8 @@
       <c r="K634" t="s">
         <v>13</v>
       </c>
-      <c r="O634" s="2"/>
-    </row>
-    <row r="635" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="635" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A635" t="s">
         <v>11</v>
       </c>
@@ -28421,9 +27798,8 @@
       <c r="K635" t="s">
         <v>13</v>
       </c>
-      <c r="O635" s="2"/>
-    </row>
-    <row r="636" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="636" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A636" t="s">
         <v>11</v>
       </c>
@@ -28457,9 +27833,8 @@
       <c r="K636" t="s">
         <v>13</v>
       </c>
-      <c r="O636" s="2"/>
-    </row>
-    <row r="637" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="637" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A637" t="s">
         <v>11</v>
       </c>
@@ -28493,9 +27868,8 @@
       <c r="K637" t="s">
         <v>13</v>
       </c>
-      <c r="O637" s="2"/>
-    </row>
-    <row r="638" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="638" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A638" t="s">
         <v>11</v>
       </c>
@@ -28529,9 +27903,8 @@
       <c r="K638" t="s">
         <v>13</v>
       </c>
-      <c r="O638" s="2"/>
-    </row>
-    <row r="639" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="639" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A639" t="s">
         <v>11</v>
       </c>
@@ -28565,9 +27938,8 @@
       <c r="K639" t="s">
         <v>13</v>
       </c>
-      <c r="O639" s="2"/>
-    </row>
-    <row r="640" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="640" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A640" t="s">
         <v>11</v>
       </c>
@@ -28601,9 +27973,8 @@
       <c r="K640" t="s">
         <v>13</v>
       </c>
-      <c r="O640" s="2"/>
-    </row>
-    <row r="641" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="641" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A641" t="s">
         <v>11</v>
       </c>
@@ -28637,9 +28008,8 @@
       <c r="K641" t="s">
         <v>13</v>
       </c>
-      <c r="O641" s="2"/>
-    </row>
-    <row r="642" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="642" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A642" t="s">
         <v>11</v>
       </c>
@@ -28673,9 +28043,8 @@
       <c r="K642" t="s">
         <v>13</v>
       </c>
-      <c r="O642" s="2"/>
-    </row>
-    <row r="643" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="643" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A643" t="s">
         <v>11</v>
       </c>
@@ -28709,9 +28078,8 @@
       <c r="K643" t="s">
         <v>13</v>
       </c>
-      <c r="O643" s="2"/>
-    </row>
-    <row r="644" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="644" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A644" t="s">
         <v>11</v>
       </c>
@@ -28745,9 +28113,8 @@
       <c r="K644" t="s">
         <v>13</v>
       </c>
-      <c r="O644" s="2"/>
-    </row>
-    <row r="645" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="645" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A645" t="s">
         <v>11</v>
       </c>
@@ -28781,9 +28148,8 @@
       <c r="K645" t="s">
         <v>13</v>
       </c>
-      <c r="O645" s="2"/>
-    </row>
-    <row r="646" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="646" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A646" t="s">
         <v>11</v>
       </c>
@@ -28817,9 +28183,8 @@
       <c r="K646" t="s">
         <v>13</v>
       </c>
-      <c r="O646" s="2"/>
-    </row>
-    <row r="647" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="647" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A647" t="s">
         <v>11</v>
       </c>
@@ -28853,9 +28218,8 @@
       <c r="K647" t="s">
         <v>13</v>
       </c>
-      <c r="O647" s="2"/>
-    </row>
-    <row r="648" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="648" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A648" t="s">
         <v>11</v>
       </c>
@@ -28889,9 +28253,8 @@
       <c r="K648" t="s">
         <v>13</v>
       </c>
-      <c r="O648" s="2"/>
-    </row>
-    <row r="649" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="649" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A649" t="s">
         <v>11</v>
       </c>
@@ -28925,9 +28288,8 @@
       <c r="K649" t="s">
         <v>13</v>
       </c>
-      <c r="O649" s="2"/>
-    </row>
-    <row r="650" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="650" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A650" t="s">
         <v>11</v>
       </c>
@@ -28961,9 +28323,8 @@
       <c r="K650" t="s">
         <v>13</v>
       </c>
-      <c r="O650" s="2"/>
-    </row>
-    <row r="651" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="651" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A651" t="s">
         <v>11</v>
       </c>
@@ -28997,9 +28358,8 @@
       <c r="K651" t="s">
         <v>13</v>
       </c>
-      <c r="O651" s="2"/>
-    </row>
-    <row r="652" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="652" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A652" t="s">
         <v>11</v>
       </c>
@@ -29033,9 +28393,8 @@
       <c r="K652" t="s">
         <v>13</v>
       </c>
-      <c r="O652" s="2"/>
-    </row>
-    <row r="653" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="653" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A653" t="s">
         <v>11</v>
       </c>
@@ -29069,9 +28428,8 @@
       <c r="K653" t="s">
         <v>13</v>
       </c>
-      <c r="O653" s="2"/>
-    </row>
-    <row r="654" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="654" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A654" t="s">
         <v>11</v>
       </c>
@@ -29105,9 +28463,8 @@
       <c r="K654" t="s">
         <v>13</v>
       </c>
-      <c r="O654" s="2"/>
-    </row>
-    <row r="655" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="655" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A655" t="s">
         <v>11</v>
       </c>
@@ -29141,9 +28498,8 @@
       <c r="K655" t="s">
         <v>1364</v>
       </c>
-      <c r="O655" s="2"/>
-    </row>
-    <row r="656" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="656" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A656" t="s">
         <v>11</v>
       </c>
@@ -29177,9 +28533,8 @@
       <c r="K656" t="s">
         <v>13</v>
       </c>
-      <c r="O656" s="2"/>
-    </row>
-    <row r="657" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="657" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A657" t="s">
         <v>11</v>
       </c>
@@ -29213,9 +28568,8 @@
       <c r="K657" t="s">
         <v>13</v>
       </c>
-      <c r="O657" s="2"/>
-    </row>
-    <row r="658" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="658" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A658" t="s">
         <v>11</v>
       </c>
@@ -29249,9 +28603,8 @@
       <c r="K658" t="s">
         <v>13</v>
       </c>
-      <c r="O658" s="2"/>
-    </row>
-    <row r="659" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="659" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A659" t="s">
         <v>11</v>
       </c>
@@ -29285,9 +28638,8 @@
       <c r="K659" t="s">
         <v>13</v>
       </c>
-      <c r="O659" s="2"/>
-    </row>
-    <row r="660" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="660" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A660" t="s">
         <v>11</v>
       </c>
@@ -29321,9 +28673,8 @@
       <c r="K660" t="s">
         <v>13</v>
       </c>
-      <c r="O660" s="2"/>
-    </row>
-    <row r="661" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="661" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A661" t="s">
         <v>11</v>
       </c>
@@ -29357,9 +28708,8 @@
       <c r="K661" t="s">
         <v>13</v>
       </c>
-      <c r="O661" s="2"/>
-    </row>
-    <row r="662" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="662" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A662" t="s">
         <v>11</v>
       </c>
@@ -29393,9 +28743,8 @@
       <c r="K662" t="s">
         <v>13</v>
       </c>
-      <c r="O662" s="2"/>
-    </row>
-    <row r="663" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="663" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A663" t="s">
         <v>11</v>
       </c>
@@ -29429,9 +28778,8 @@
       <c r="K663" t="s">
         <v>13</v>
       </c>
-      <c r="O663" s="2"/>
-    </row>
-    <row r="664" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="664" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A664" t="s">
         <v>11</v>
       </c>
@@ -29465,9 +28813,8 @@
       <c r="K664" t="s">
         <v>13</v>
       </c>
-      <c r="O664" s="2"/>
-    </row>
-    <row r="665" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="665" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A665" t="s">
         <v>11</v>
       </c>
@@ -29501,9 +28848,8 @@
       <c r="K665" t="s">
         <v>13</v>
       </c>
-      <c r="O665" s="2"/>
-    </row>
-    <row r="666" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="666" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A666" t="s">
         <v>11</v>
       </c>
@@ -29537,9 +28883,8 @@
       <c r="K666" t="s">
         <v>13</v>
       </c>
-      <c r="O666" s="2"/>
-    </row>
-    <row r="667" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="667" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A667" t="s">
         <v>11</v>
       </c>
@@ -29573,9 +28918,8 @@
       <c r="K667" t="s">
         <v>13</v>
       </c>
-      <c r="O667" s="2"/>
-    </row>
-    <row r="668" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="668" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A668" t="s">
         <v>11</v>
       </c>
@@ -29609,9 +28953,8 @@
       <c r="K668" t="s">
         <v>13</v>
       </c>
-      <c r="O668" s="2"/>
-    </row>
-    <row r="669" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="669" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A669" t="s">
         <v>11</v>
       </c>
@@ -29645,9 +28988,8 @@
       <c r="K669" t="s">
         <v>13</v>
       </c>
-      <c r="O669" s="2"/>
-    </row>
-    <row r="670" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="670" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A670" t="s">
         <v>11</v>
       </c>
@@ -29681,9 +29023,8 @@
       <c r="K670" t="s">
         <v>13</v>
       </c>
-      <c r="O670" s="2"/>
-    </row>
-    <row r="671" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="671" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A671" t="s">
         <v>11</v>
       </c>
@@ -29717,9 +29058,8 @@
       <c r="K671" t="s">
         <v>13</v>
       </c>
-      <c r="O671" s="2"/>
-    </row>
-    <row r="672" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="672" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A672" t="s">
         <v>11</v>
       </c>
@@ -29753,9 +29093,8 @@
       <c r="K672" t="s">
         <v>13</v>
       </c>
-      <c r="O672" s="2"/>
-    </row>
-    <row r="673" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="673" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A673" t="s">
         <v>11</v>
       </c>
@@ -29789,9 +29128,8 @@
       <c r="K673" t="s">
         <v>13</v>
       </c>
-      <c r="O673" s="2"/>
-    </row>
-    <row r="674" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="674" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A674" t="s">
         <v>11</v>
       </c>
@@ -29825,9 +29163,8 @@
       <c r="K674" t="s">
         <v>13</v>
       </c>
-      <c r="O674" s="2"/>
-    </row>
-    <row r="675" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="675" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A675" t="s">
         <v>11</v>
       </c>
@@ -29861,9 +29198,8 @@
       <c r="K675" t="s">
         <v>13</v>
       </c>
-      <c r="O675" s="2"/>
-    </row>
-    <row r="676" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="676" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A676" t="s">
         <v>11</v>
       </c>
@@ -29897,9 +29233,8 @@
       <c r="K676" t="s">
         <v>13</v>
       </c>
-      <c r="O676" s="2"/>
-    </row>
-    <row r="677" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="677" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A677" t="s">
         <v>11</v>
       </c>
@@ -29933,9 +29268,8 @@
       <c r="K677" t="s">
         <v>13</v>
       </c>
-      <c r="O677" s="2"/>
-    </row>
-    <row r="678" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="678" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A678" t="s">
         <v>11</v>
       </c>
@@ -29969,9 +29303,8 @@
       <c r="K678" t="s">
         <v>13</v>
       </c>
-      <c r="O678" s="2"/>
-    </row>
-    <row r="679" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="679" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A679" t="s">
         <v>11</v>
       </c>
@@ -30005,9 +29338,8 @@
       <c r="K679" t="s">
         <v>13</v>
       </c>
-      <c r="O679" s="2"/>
-    </row>
-    <row r="680" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="680" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A680" t="s">
         <v>11</v>
       </c>
@@ -30041,9 +29373,8 @@
       <c r="K680" t="s">
         <v>13</v>
       </c>
-      <c r="O680" s="2"/>
-    </row>
-    <row r="681" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="681" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A681" t="s">
         <v>11</v>
       </c>
@@ -30077,9 +29408,8 @@
       <c r="K681" t="s">
         <v>13</v>
       </c>
-      <c r="O681" s="2"/>
-    </row>
-    <row r="682" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="682" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A682" t="s">
         <v>11</v>
       </c>
@@ -30113,9 +29443,8 @@
       <c r="K682" t="s">
         <v>13</v>
       </c>
-      <c r="O682" s="2"/>
-    </row>
-    <row r="683" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="683" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A683" t="s">
         <v>11</v>
       </c>
@@ -30149,9 +29478,8 @@
       <c r="K683" t="s">
         <v>13</v>
       </c>
-      <c r="O683" s="2"/>
-    </row>
-    <row r="684" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="684" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A684" t="s">
         <v>98</v>
       </c>
@@ -30185,9 +29513,8 @@
       <c r="K684" t="s">
         <v>13</v>
       </c>
-      <c r="O684" s="2"/>
-    </row>
-    <row r="685" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="685" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A685" t="s">
         <v>11</v>
       </c>
@@ -30221,9 +29548,8 @@
       <c r="K685" t="s">
         <v>13</v>
       </c>
-      <c r="O685" s="2"/>
-    </row>
-    <row r="686" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="686" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A686" t="s">
         <v>98</v>
       </c>
@@ -30257,9 +29583,8 @@
       <c r="K686" t="s">
         <v>13</v>
       </c>
-      <c r="O686" s="2"/>
-    </row>
-    <row r="687" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="687" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A687" t="s">
         <v>11</v>
       </c>
@@ -30293,9 +29618,8 @@
       <c r="K687" t="s">
         <v>13</v>
       </c>
-      <c r="O687" s="2"/>
-    </row>
-    <row r="688" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="688" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A688" t="s">
         <v>11</v>
       </c>
@@ -30329,9 +29653,8 @@
       <c r="K688" t="s">
         <v>13</v>
       </c>
-      <c r="O688" s="2"/>
-    </row>
-    <row r="689" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="689" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A689" t="s">
         <v>11</v>
       </c>
@@ -30365,9 +29688,8 @@
       <c r="K689" t="s">
         <v>13</v>
       </c>
-      <c r="O689" s="2"/>
-    </row>
-    <row r="690" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="690" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A690" t="s">
         <v>11</v>
       </c>
@@ -30401,9 +29723,8 @@
       <c r="K690" t="s">
         <v>13</v>
       </c>
-      <c r="O690" s="2"/>
-    </row>
-    <row r="691" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="691" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A691" t="s">
         <v>11</v>
       </c>
@@ -30437,9 +29758,8 @@
       <c r="K691" t="s">
         <v>13</v>
       </c>
-      <c r="O691" s="2"/>
-    </row>
-    <row r="692" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="692" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A692" t="s">
         <v>11</v>
       </c>
@@ -30473,9 +29793,8 @@
       <c r="K692" t="s">
         <v>13</v>
       </c>
-      <c r="O692" s="2"/>
-    </row>
-    <row r="693" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="693" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A693" t="s">
         <v>11</v>
       </c>
@@ -30509,9 +29828,8 @@
       <c r="K693" t="s">
         <v>13</v>
       </c>
-      <c r="O693" s="2"/>
-    </row>
-    <row r="694" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="694" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A694" t="s">
         <v>11</v>
       </c>
@@ -30545,9 +29863,8 @@
       <c r="K694" t="s">
         <v>13</v>
       </c>
-      <c r="O694" s="2"/>
-    </row>
-    <row r="695" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="695" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A695" t="s">
         <v>11</v>
       </c>
@@ -30581,9 +29898,8 @@
       <c r="K695" t="s">
         <v>13</v>
       </c>
-      <c r="O695" s="2"/>
-    </row>
-    <row r="696" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="696" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A696" t="s">
         <v>11</v>
       </c>
@@ -30617,9 +29933,8 @@
       <c r="K696" t="s">
         <v>13</v>
       </c>
-      <c r="O696" s="2"/>
-    </row>
-    <row r="697" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="697" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A697" t="s">
         <v>11</v>
       </c>
@@ -30653,9 +29968,8 @@
       <c r="K697" t="s">
         <v>13</v>
       </c>
-      <c r="O697" s="2"/>
-    </row>
-    <row r="698" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="698" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A698" t="s">
         <v>11</v>
       </c>
@@ -30689,9 +30003,8 @@
       <c r="K698" t="s">
         <v>13</v>
       </c>
-      <c r="O698" s="2"/>
-    </row>
-    <row r="699" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="699" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A699" t="s">
         <v>11</v>
       </c>
@@ -30725,9 +30038,8 @@
       <c r="K699" t="s">
         <v>13</v>
       </c>
-      <c r="O699" s="2"/>
-    </row>
-    <row r="700" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="700" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A700" t="s">
         <v>11</v>
       </c>
@@ -30761,9 +30073,8 @@
       <c r="K700" t="s">
         <v>13</v>
       </c>
-      <c r="O700" s="2"/>
-    </row>
-    <row r="701" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="701" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A701" t="s">
         <v>11</v>
       </c>
@@ -30797,9 +30108,8 @@
       <c r="K701" t="s">
         <v>13</v>
       </c>
-      <c r="O701" s="2"/>
-    </row>
-    <row r="702" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="702" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A702" t="s">
         <v>11</v>
       </c>
@@ -30833,9 +30143,8 @@
       <c r="K702" t="s">
         <v>13</v>
       </c>
-      <c r="O702" s="2"/>
-    </row>
-    <row r="703" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="703" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A703" t="s">
         <v>11</v>
       </c>
@@ -30869,9 +30178,8 @@
       <c r="K703" t="s">
         <v>13</v>
       </c>
-      <c r="O703" s="2"/>
-    </row>
-    <row r="704" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="704" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A704" t="s">
         <v>11</v>
       </c>
@@ -30905,9 +30213,8 @@
       <c r="K704" t="s">
         <v>13</v>
       </c>
-      <c r="O704" s="2"/>
-    </row>
-    <row r="705" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="705" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A705" t="s">
         <v>11</v>
       </c>
@@ -30941,9 +30248,8 @@
       <c r="K705" t="s">
         <v>13</v>
       </c>
-      <c r="O705" s="2"/>
-    </row>
-    <row r="706" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="706" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A706" t="s">
         <v>11</v>
       </c>
@@ -30977,9 +30283,8 @@
       <c r="K706" t="s">
         <v>13</v>
       </c>
-      <c r="O706" s="2"/>
-    </row>
-    <row r="707" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="707" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A707" t="s">
         <v>11</v>
       </c>
@@ -31013,9 +30318,8 @@
       <c r="K707" t="s">
         <v>13</v>
       </c>
-      <c r="O707" s="2"/>
-    </row>
-    <row r="708" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="708" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A708" t="s">
         <v>11</v>
       </c>
@@ -31049,9 +30353,8 @@
       <c r="K708" t="s">
         <v>13</v>
       </c>
-      <c r="O708" s="2"/>
-    </row>
-    <row r="709" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="709" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A709" t="s">
         <v>11</v>
       </c>
@@ -31085,9 +30388,8 @@
       <c r="K709" t="s">
         <v>13</v>
       </c>
-      <c r="O709" s="2"/>
-    </row>
-    <row r="710" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="710" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A710" t="s">
         <v>11</v>
       </c>
@@ -31121,9 +30423,8 @@
       <c r="K710" t="s">
         <v>13</v>
       </c>
-      <c r="O710" s="2"/>
-    </row>
-    <row r="711" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="711" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A711" t="s">
         <v>11</v>
       </c>
@@ -31157,9 +30458,8 @@
       <c r="K711" t="s">
         <v>13</v>
       </c>
-      <c r="O711" s="2"/>
-    </row>
-    <row r="712" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="712" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A712" t="s">
         <v>11</v>
       </c>
@@ -31193,9 +30493,8 @@
       <c r="K712" t="s">
         <v>13</v>
       </c>
-      <c r="O712" s="2"/>
-    </row>
-    <row r="713" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="713" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A713" t="s">
         <v>11</v>
       </c>
@@ -31229,9 +30528,8 @@
       <c r="K713" t="s">
         <v>13</v>
       </c>
-      <c r="O713" s="2"/>
-    </row>
-    <row r="714" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="714" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A714" t="s">
         <v>11</v>
       </c>
@@ -31265,9 +30563,8 @@
       <c r="K714" t="s">
         <v>13</v>
       </c>
-      <c r="O714" s="2"/>
-    </row>
-    <row r="715" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="715" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A715" t="s">
         <v>11</v>
       </c>
@@ -31301,9 +30598,8 @@
       <c r="K715" t="s">
         <v>13</v>
       </c>
-      <c r="O715" s="2"/>
-    </row>
-    <row r="716" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="716" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A716" t="s">
         <v>11</v>
       </c>
@@ -31337,9 +30633,8 @@
       <c r="K716" t="s">
         <v>13</v>
       </c>
-      <c r="O716" s="2"/>
-    </row>
-    <row r="717" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="717" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A717" t="s">
         <v>11</v>
       </c>
@@ -31373,9 +30668,8 @@
       <c r="K717" t="s">
         <v>13</v>
       </c>
-      <c r="O717" s="2"/>
-    </row>
-    <row r="718" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="718" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A718" t="s">
         <v>11</v>
       </c>
@@ -31409,9 +30703,8 @@
       <c r="K718" t="s">
         <v>13</v>
       </c>
-      <c r="O718" s="2"/>
-    </row>
-    <row r="719" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="719" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A719" t="s">
         <v>11</v>
       </c>
@@ -31445,9 +30738,8 @@
       <c r="K719" t="s">
         <v>13</v>
       </c>
-      <c r="O719" s="2"/>
-    </row>
-    <row r="720" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="720" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A720" t="s">
         <v>11</v>
       </c>
@@ -31481,9 +30773,8 @@
       <c r="K720" t="s">
         <v>13</v>
       </c>
-      <c r="O720" s="2"/>
-    </row>
-    <row r="721" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="721" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A721" t="s">
         <v>11</v>
       </c>
@@ -31517,9 +30808,8 @@
       <c r="K721" t="s">
         <v>13</v>
       </c>
-      <c r="O721" s="2"/>
-    </row>
-    <row r="722" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="722" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A722" t="s">
         <v>11</v>
       </c>
@@ -31553,9 +30843,8 @@
       <c r="K722" t="s">
         <v>13</v>
       </c>
-      <c r="O722" s="2"/>
-    </row>
-    <row r="723" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="723" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A723" t="s">
         <v>11</v>
       </c>
@@ -31589,9 +30878,8 @@
       <c r="K723" t="s">
         <v>13</v>
       </c>
-      <c r="O723" s="2"/>
-    </row>
-    <row r="724" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="724" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A724" t="s">
         <v>11</v>
       </c>
@@ -31625,9 +30913,8 @@
       <c r="K724" t="s">
         <v>13</v>
       </c>
-      <c r="O724" s="2"/>
-    </row>
-    <row r="725" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="725" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A725" t="s">
         <v>11</v>
       </c>
@@ -31661,9 +30948,8 @@
       <c r="K725" t="s">
         <v>13</v>
       </c>
-      <c r="O725" s="2"/>
-    </row>
-    <row r="726" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="726" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A726" t="s">
         <v>11</v>
       </c>
@@ -31697,9 +30983,8 @@
       <c r="K726" t="s">
         <v>13</v>
       </c>
-      <c r="O726" s="2"/>
-    </row>
-    <row r="727" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="727" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A727" t="s">
         <v>11</v>
       </c>
@@ -31733,9 +31018,8 @@
       <c r="K727" t="s">
         <v>13</v>
       </c>
-      <c r="O727" s="2"/>
-    </row>
-    <row r="728" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="728" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A728" t="s">
         <v>11</v>
       </c>
@@ -31769,9 +31053,8 @@
       <c r="K728" t="s">
         <v>13</v>
       </c>
-      <c r="O728" s="2"/>
-    </row>
-    <row r="729" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="729" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A729" t="s">
         <v>11</v>
       </c>
@@ -31805,9 +31088,8 @@
       <c r="K729" t="s">
         <v>13</v>
       </c>
-      <c r="O729" s="2"/>
-    </row>
-    <row r="730" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="730" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A730" t="s">
         <v>11</v>
       </c>
@@ -31841,9 +31123,8 @@
       <c r="K730" t="s">
         <v>13</v>
       </c>
-      <c r="O730" s="2"/>
-    </row>
-    <row r="731" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="731" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A731" t="s">
         <v>11</v>
       </c>
@@ -31877,9 +31158,8 @@
       <c r="K731" t="s">
         <v>13</v>
       </c>
-      <c r="O731" s="2"/>
-    </row>
-    <row r="732" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="732" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A732" t="s">
         <v>11</v>
       </c>
@@ -31913,9 +31193,8 @@
       <c r="K732" t="s">
         <v>13</v>
       </c>
-      <c r="O732" s="2"/>
-    </row>
-    <row r="733" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="733" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A733" t="s">
         <v>11</v>
       </c>
@@ -31949,9 +31228,8 @@
       <c r="K733" t="s">
         <v>13</v>
       </c>
-      <c r="O733" s="2"/>
-    </row>
-    <row r="734" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="734" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A734" t="s">
         <v>11</v>
       </c>
@@ -31985,9 +31263,8 @@
       <c r="K734" t="s">
         <v>13</v>
       </c>
-      <c r="O734" s="2"/>
-    </row>
-    <row r="735" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="735" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A735" t="s">
         <v>11</v>
       </c>
@@ -32021,9 +31298,8 @@
       <c r="K735" t="s">
         <v>13</v>
       </c>
-      <c r="O735" s="2"/>
-    </row>
-    <row r="736" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="736" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A736" t="s">
         <v>11</v>
       </c>
@@ -32057,9 +31333,8 @@
       <c r="K736" t="s">
         <v>13</v>
       </c>
-      <c r="O736" s="2"/>
-    </row>
-    <row r="737" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="737" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A737" t="s">
         <v>11</v>
       </c>
@@ -32093,9 +31368,8 @@
       <c r="K737" t="s">
         <v>13</v>
       </c>
-      <c r="O737" s="2"/>
-    </row>
-    <row r="738" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="738" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A738" t="s">
         <v>11</v>
       </c>
@@ -32129,9 +31403,8 @@
       <c r="K738" t="s">
         <v>13</v>
       </c>
-      <c r="O738" s="2"/>
-    </row>
-    <row r="739" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="739" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A739" t="s">
         <v>11</v>
       </c>
@@ -32165,9 +31438,8 @@
       <c r="K739" t="s">
         <v>13</v>
       </c>
-      <c r="O739" s="2"/>
-    </row>
-    <row r="740" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="740" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A740" t="s">
         <v>98</v>
       </c>
@@ -32201,9 +31473,8 @@
       <c r="K740" t="s">
         <v>13</v>
       </c>
-      <c r="O740" s="2"/>
-    </row>
-    <row r="741" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="741" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A741" t="s">
         <v>11</v>
       </c>
@@ -32237,9 +31508,8 @@
       <c r="K741" t="s">
         <v>13</v>
       </c>
-      <c r="O741" s="2"/>
-    </row>
-    <row r="742" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="742" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A742" t="s">
         <v>11</v>
       </c>
@@ -32273,9 +31543,8 @@
       <c r="K742" t="s">
         <v>13</v>
       </c>
-      <c r="O742" s="2"/>
-    </row>
-    <row r="743" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="743" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A743" t="s">
         <v>11</v>
       </c>
@@ -32309,9 +31578,8 @@
       <c r="K743" t="s">
         <v>13</v>
       </c>
-      <c r="O743" s="2"/>
-    </row>
-    <row r="744" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="744" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A744" t="s">
         <v>11</v>
       </c>
@@ -32345,9 +31613,8 @@
       <c r="K744" t="s">
         <v>13</v>
       </c>
-      <c r="O744" s="2"/>
-    </row>
-    <row r="745" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="745" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A745" t="s">
         <v>11</v>
       </c>
@@ -32381,9 +31648,8 @@
       <c r="K745" t="s">
         <v>13</v>
       </c>
-      <c r="O745" s="2"/>
-    </row>
-    <row r="746" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="746" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A746" t="s">
         <v>11</v>
       </c>
@@ -32417,9 +31683,8 @@
       <c r="K746" t="s">
         <v>13</v>
       </c>
-      <c r="O746" s="2"/>
-    </row>
-    <row r="747" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="747" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A747" t="s">
         <v>11</v>
       </c>
@@ -32453,9 +31718,8 @@
       <c r="K747" t="s">
         <v>13</v>
       </c>
-      <c r="O747" s="2"/>
-    </row>
-    <row r="748" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="748" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A748" t="s">
         <v>11</v>
       </c>
@@ -32489,9 +31753,8 @@
       <c r="K748" t="s">
         <v>13</v>
       </c>
-      <c r="O748" s="2"/>
-    </row>
-    <row r="749" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="749" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A749" t="s">
         <v>11</v>
       </c>
@@ -32525,9 +31788,8 @@
       <c r="K749" t="s">
         <v>13</v>
       </c>
-      <c r="O749" s="2"/>
-    </row>
-    <row r="750" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="750" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A750" t="s">
         <v>11</v>
       </c>
@@ -32561,9 +31823,8 @@
       <c r="K750" t="s">
         <v>13</v>
       </c>
-      <c r="O750" s="2"/>
-    </row>
-    <row r="751" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="751" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A751" t="s">
         <v>11</v>
       </c>
@@ -32597,9 +31858,8 @@
       <c r="K751" t="s">
         <v>13</v>
       </c>
-      <c r="O751" s="2"/>
-    </row>
-    <row r="752" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="752" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A752" t="s">
         <v>11</v>
       </c>
@@ -32633,9 +31893,8 @@
       <c r="K752" t="s">
         <v>13</v>
       </c>
-      <c r="O752" s="2"/>
-    </row>
-    <row r="753" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="753" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A753" t="s">
         <v>11</v>
       </c>
@@ -32669,9 +31928,8 @@
       <c r="K753" t="s">
         <v>13</v>
       </c>
-      <c r="O753" s="2"/>
-    </row>
-    <row r="754" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="754" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A754" t="s">
         <v>11</v>
       </c>
@@ -32705,9 +31963,8 @@
       <c r="K754" t="s">
         <v>13</v>
       </c>
-      <c r="O754" s="2"/>
-    </row>
-    <row r="755" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="755" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A755" t="s">
         <v>11</v>
       </c>
@@ -32741,9 +31998,8 @@
       <c r="K755" t="s">
         <v>13</v>
       </c>
-      <c r="O755" s="2"/>
-    </row>
-    <row r="756" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="756" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A756" t="s">
         <v>11</v>
       </c>
@@ -32777,9 +32033,8 @@
       <c r="K756" t="s">
         <v>13</v>
       </c>
-      <c r="O756" s="2"/>
-    </row>
-    <row r="757" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="757" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A757" t="s">
         <v>11</v>
       </c>
@@ -32813,9 +32068,8 @@
       <c r="K757" t="s">
         <v>13</v>
       </c>
-      <c r="O757" s="2"/>
-    </row>
-    <row r="758" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="758" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A758" t="s">
         <v>11</v>
       </c>
@@ -32849,9 +32103,8 @@
       <c r="K758" t="s">
         <v>13</v>
       </c>
-      <c r="O758" s="2"/>
-    </row>
-    <row r="759" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="759" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A759" t="s">
         <v>11</v>
       </c>
@@ -32885,9 +32138,8 @@
       <c r="K759" t="s">
         <v>13</v>
       </c>
-      <c r="O759" s="2"/>
-    </row>
-    <row r="760" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="760" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A760" t="s">
         <v>11</v>
       </c>
@@ -32921,9 +32173,8 @@
       <c r="K760" t="s">
         <v>13</v>
       </c>
-      <c r="O760" s="2"/>
-    </row>
-    <row r="761" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="761" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A761" t="s">
         <v>11</v>
       </c>
@@ -32957,9 +32208,8 @@
       <c r="K761" t="s">
         <v>13</v>
       </c>
-      <c r="O761" s="2"/>
-    </row>
-    <row r="762" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="762" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A762" t="s">
         <v>11</v>
       </c>
@@ -32993,9 +32243,8 @@
       <c r="K762" t="s">
         <v>13</v>
       </c>
-      <c r="O762" s="2"/>
-    </row>
-    <row r="763" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="763" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A763" t="s">
         <v>11</v>
       </c>
@@ -33029,9 +32278,8 @@
       <c r="K763" t="s">
         <v>13</v>
       </c>
-      <c r="O763" s="2"/>
-    </row>
-    <row r="764" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="764" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A764" t="s">
         <v>98</v>
       </c>
@@ -33065,9 +32313,8 @@
       <c r="K764" t="s">
         <v>13</v>
       </c>
-      <c r="O764" s="2"/>
-    </row>
-    <row r="765" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="765" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A765" t="s">
         <v>11</v>
       </c>
@@ -33101,9 +32348,8 @@
       <c r="K765" t="s">
         <v>13</v>
       </c>
-      <c r="O765" s="2"/>
-    </row>
-    <row r="766" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="766" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A766" t="s">
         <v>11</v>
       </c>
@@ -33137,9 +32383,8 @@
       <c r="K766" t="s">
         <v>13</v>
       </c>
-      <c r="O766" s="2"/>
-    </row>
-    <row r="767" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="767" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A767" t="s">
         <v>11</v>
       </c>
@@ -33173,9 +32418,8 @@
       <c r="K767" t="s">
         <v>13</v>
       </c>
-      <c r="O767" s="2"/>
-    </row>
-    <row r="768" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="768" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A768" t="s">
         <v>11</v>
       </c>
@@ -33209,9 +32453,8 @@
       <c r="K768" t="s">
         <v>13</v>
       </c>
-      <c r="O768" s="2"/>
-    </row>
-    <row r="769" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="769" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A769" t="s">
         <v>11</v>
       </c>
@@ -33245,9 +32488,8 @@
       <c r="K769" t="s">
         <v>13</v>
       </c>
-      <c r="O769" s="2"/>
-    </row>
-    <row r="770" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="770" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A770" t="s">
         <v>11</v>
       </c>
@@ -33281,9 +32523,8 @@
       <c r="K770" t="s">
         <v>13</v>
       </c>
-      <c r="O770" s="2"/>
-    </row>
-    <row r="771" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="771" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A771" t="s">
         <v>11</v>
       </c>
@@ -33317,9 +32558,8 @@
       <c r="K771" t="s">
         <v>13</v>
       </c>
-      <c r="O771" s="2"/>
-    </row>
-    <row r="772" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="772" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A772" t="s">
         <v>11</v>
       </c>
@@ -33353,9 +32593,8 @@
       <c r="K772" t="s">
         <v>13</v>
       </c>
-      <c r="O772" s="2"/>
-    </row>
-    <row r="773" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="773" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A773" t="s">
         <v>11</v>
       </c>
@@ -33389,9 +32628,8 @@
       <c r="K773" t="s">
         <v>13</v>
       </c>
-      <c r="O773" s="2"/>
-    </row>
-    <row r="774" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="774" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A774" t="s">
         <v>11</v>
       </c>
@@ -33425,9 +32663,8 @@
       <c r="K774" t="s">
         <v>13</v>
       </c>
-      <c r="O774" s="2"/>
-    </row>
-    <row r="775" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="775" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A775" t="s">
         <v>11</v>
       </c>
@@ -33461,9 +32698,8 @@
       <c r="K775" t="s">
         <v>13</v>
       </c>
-      <c r="O775" s="2"/>
-    </row>
-    <row r="776" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="776" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A776" t="s">
         <v>11</v>
       </c>
@@ -33497,9 +32733,8 @@
       <c r="K776" t="s">
         <v>13</v>
       </c>
-      <c r="O776" s="2"/>
-    </row>
-    <row r="777" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="777" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A777" t="s">
         <v>11</v>
       </c>
@@ -33533,9 +32768,8 @@
       <c r="K777" t="s">
         <v>13</v>
       </c>
-      <c r="O777" s="2"/>
-    </row>
-    <row r="778" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="778" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A778" t="s">
         <v>11</v>
       </c>
@@ -33569,9 +32803,8 @@
       <c r="K778" t="s">
         <v>13</v>
       </c>
-      <c r="O778" s="2"/>
-    </row>
-    <row r="779" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="779" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A779" t="s">
         <v>11</v>
       </c>
@@ -33605,9 +32838,8 @@
       <c r="K779" t="s">
         <v>13</v>
       </c>
-      <c r="O779" s="2"/>
-    </row>
-    <row r="780" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="780" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A780" t="s">
         <v>11</v>
       </c>
@@ -33641,9 +32873,8 @@
       <c r="K780" t="s">
         <v>13</v>
       </c>
-      <c r="O780" s="2"/>
-    </row>
-    <row r="781" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="781" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A781" t="s">
         <v>11</v>
       </c>
@@ -33677,9 +32908,8 @@
       <c r="K781" t="s">
         <v>13</v>
       </c>
-      <c r="O781" s="2"/>
-    </row>
-    <row r="782" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="782" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A782" t="s">
         <v>11</v>
       </c>
@@ -33713,9 +32943,8 @@
       <c r="K782" t="s">
         <v>13</v>
       </c>
-      <c r="O782" s="2"/>
-    </row>
-    <row r="783" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="783" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A783" t="s">
         <v>11</v>
       </c>
@@ -33749,9 +32978,8 @@
       <c r="K783" t="s">
         <v>13</v>
       </c>
-      <c r="O783" s="2"/>
-    </row>
-    <row r="784" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="784" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A784" t="s">
         <v>11</v>
       </c>
@@ -33785,7 +33013,6 @@
       <c r="K784" t="s">
         <v>13</v>
       </c>
-      <c r="O784" s="2"/>
     </row>
     <row r="785" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A785" t="s">
@@ -33821,7 +33048,6 @@
       <c r="K785" t="s">
         <v>13</v>
       </c>
-      <c r="O785" s="2"/>
     </row>
     <row r="786" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A786" t="s">
@@ -33857,7 +33083,6 @@
       <c r="K786" t="s">
         <v>13</v>
       </c>
-      <c r="O786" s="2"/>
     </row>
     <row r="787" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A787" t="s">
@@ -33893,7 +33118,6 @@
       <c r="K787" t="s">
         <v>13</v>
       </c>
-      <c r="O787" s="2"/>
     </row>
     <row r="788" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A788" t="s">
@@ -33929,7 +33153,6 @@
       <c r="K788" t="s">
         <v>13</v>
       </c>
-      <c r="O788" s="2"/>
     </row>
     <row r="789" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A789" t="s">
@@ -33965,7 +33188,6 @@
       <c r="K789" t="s">
         <v>13</v>
       </c>
-      <c r="O789" s="2"/>
     </row>
     <row r="790" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A790" t="s">
@@ -34001,7 +33223,6 @@
       <c r="K790" t="s">
         <v>13</v>
       </c>
-      <c r="O790" s="2"/>
     </row>
     <row r="791" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A791" t="s">
@@ -34037,7 +33258,6 @@
       <c r="K791" t="s">
         <v>13</v>
       </c>
-      <c r="O791" s="2"/>
     </row>
     <row r="792" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A792" t="s">
@@ -34073,7 +33293,6 @@
       <c r="K792" t="s">
         <v>13</v>
       </c>
-      <c r="O792" s="2"/>
     </row>
     <row r="793" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A793" t="s">
@@ -34109,7 +33328,6 @@
       <c r="K793" t="s">
         <v>13</v>
       </c>
-      <c r="O793" s="2"/>
     </row>
     <row r="794" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A794" t="s">
@@ -34145,7 +33363,6 @@
       <c r="K794" t="s">
         <v>13</v>
       </c>
-      <c r="O794" s="2"/>
     </row>
     <row r="795" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A795" t="s">
@@ -34181,7 +33398,6 @@
       <c r="K795" t="s">
         <v>13</v>
       </c>
-      <c r="O795" s="2"/>
     </row>
     <row r="796" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A796" t="s">
@@ -34205,7 +33421,27 @@
       <c r="N796" t="s">
         <v>1659</v>
       </c>
-      <c r="O796" s="2"/>
+    </row>
+    <row r="797" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A797" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B797" s="2" t="s">
+        <v>1668</v>
+      </c>
+      <c r="C797" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D797" s="2"/>
+      <c r="F797" s="2"/>
+      <c r="G797" s="2"/>
+      <c r="H797" s="2"/>
+      <c r="J797" s="2"/>
+      <c r="K797" s="2"/>
+      <c r="L797" s="2"/>
+      <c r="M797" s="2"/>
+      <c r="N797" s="2"/>
+      <c r="O797" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/data/bars.xlsx
+++ b/data/bars.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Natha\projects_and_clubs\Queen-s-Engineering-Jacket-GPA-Planner\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944C26D7-01CC-4964-8B38-4411D6FF6379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E96B334-0B54-4F6D-8CED-E4B30C7F0713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1C6F1F17-E6F1-46B7-9E88-A2681932F042}"/>
   </bookViews>
@@ -33086,7 +33086,7 @@
     </row>
     <row r="787" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A787" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="B787" t="s">
         <v>1635</v>
